--- a/study_methods/헌법_공부방법.xlsx
+++ b/study_methods/헌법_공부방법.xlsx
@@ -17,14 +17,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기타" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'전체'!$A$1:$H$121</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'기출 위주'!$A$1:$H$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'판례 정리 위주'!$A$1:$H$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'조문 암기 위주'!$A$1:$H$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'OX 문제 활용'!$A$1:$H$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'기본서 회독'!$A$1:$H$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'단권화 전략'!$A$1:$H$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'기타'!$A$1:$H$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'전체'!$A$1:$I$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'기출 위주'!$A$1:$I$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'판례 정리 위주'!$A$1:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'조문 암기 위주'!$A$1:$I$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'OX 문제 활용'!$A$1:$I$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'기본서 회독'!$A$1:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'단권화 전략'!$A$1:$I$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'기타'!$A$1:$I$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H121"/>
+  <dimension ref="A1:I121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -486,6 +486,7 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -529,6 +530,11 @@
           <t>발췌문2</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -563,6 +569,11 @@
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41696&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="55" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -593,6 +604,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40692&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=31</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="55" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -623,6 +639,11 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40688&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=32</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="55" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -661,6 +682,11 @@
           <t>10월부터 기본강의를 듣고 시험 직전에 법령특강, 최신판례특강을 들었습니다. 기본강의를 2배속으로 빠르게 듣고 듣는 중에 기출문제를 바로바로 풀었습니다. 기본강의 끝낸 후에는 기출 회독을 계속 돌렸고, 강의 중에 회독 돌리는 방법을 알려주셔서 시험 한 달 전까지는 계속 기출만 보았으며, 한 달 남았을 때는 법령과 최신판례를 같이 보았습니다. 기출을 많이 보다보면 기본서를 후에 회독 돌릴 때에는 생소한 부분만 보이기 때문에 더 빠르게 회독을 돌릴 수 있었습니다. 황남기 선생님은 특별히 외우는 방법을 알려주시지는 않지만 판례 배경 등을 설명해주셔서 더 기억에 남을 수 있었던 것 같습니다. 또한 비슷한 주제로 위헌, 합헌으로 나뉘는 판례들은 암기하기 위해 따로 노트를 만들었는데 시험 직전에 다시 정리했던 것이 실제 시험장에서 너무 큰 도움이 되었습니다.   (행정법-황남기 선생님, 함수민 선생님) 헌법을 먼저 들었기 때문에 행정법 또한 황남기 선생님을 선택해서 들었습니다. 헌법과 공부방법은 비슷하나 행정법각론 부분은 시험 3달 전에 전년도 강의를 가볍게 황남기 선생님 강의로 듣고 2달 전에는 당해연도 함수민 선생님 강의를 들었고, 시험 한 달 전부터는 각론기출문제</t>
         </is>
       </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39681&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -699,6 +725,11 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39662&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="55" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -733,6 +764,11 @@
           <t>(행정학) 행정학의 경우에는 대부분의 수험생들이 그렇듯 시험 직전까지도 가장 자신이 없었습니다. 개념의 범위가 너무 넓고 항상 불의타 문제가 나오기 때문에 대비가 어렵다고 느꼈습니다. 행정학의 경우에는 여러 이론들에 대해서 묻기 때문에 이론 간의 비교에 집중하면서 공부하는게 큰 도움이 됐습니다. 간단하게 비유하자면 단순하게 (a 이론의 특성은 키가 작다) 이런 식으로 외우면  혼동이 생길 때가 많습니다. 왜냐하면 a 이론이 b이론과 비교했을 때는 키가 작았지만, 또 다른 c이론과 비교했을 때는 키가 큰 경우가 있기 때문입니다. 행정학은 법 과목의 판례들처럼 딱 정해진 것이 아니어서 어떤 대상과 비교하냐에 따라서 해당 이론의 특성이 아 다르고 어 다르기 때문에  (a 이론은 b 이론과 비교했을 때는 키가 작다) 이런 식으로 유사한 그룹의 개념들끼리 비교를 잡으면서 개념을 유연성 있게 정리하는게 많은 도움이 됐습니다.   (헌법)) 헌법의 경우 처음 기본 강의를 들을 때는 상대적으로 재밌다고 느꼈습니다. 왜냐하면 다양한 판례들이 나오고 아무래도 판례들이 우리 생활과 밀접해 있다 보니 이러한 경우도 있구나 하면서 상대적으로 즐겁게 기본강의를 들었습니다. 하지만 기</t>
         </is>
       </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39640&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="55" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -775,6 +811,11 @@
           <t>(2) 헌법 [강의] 황남기쌤 헌법 기본이론 23년, 24년 각 1회 수강 [교재] 황남기쌤 기본서 3회독(인강 수강 포함) [교재] 황남기쌤 기출문제집 9회독 [교재] 경간 소간 국회직 등등 각종 시행처 최신기출</t>
         </is>
       </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39626&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="55" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -809,6 +850,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39624&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="55" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -851,6 +897,11 @@
           <t>2차 과목 헌법 - 신동욱 스마트헌법 기출문제풀이 행정법 - 함수민 쉬운 행정법 기출문제풀이 행정학 - 송상호 명품 행정학 단원별 문제풀이, 신경향 흐름의 주요테마 및 단원별 문제풀이 경제학 - 김종국 국(局) 경제학 기본이론, 심화이론, 7급 기출문제풀이, 국회직 기출문제풀이 모의고사 - 해커스공무원 2024 대비 제9회 7급 합격예측 모의고사</t>
         </is>
       </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39621&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="55" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -891,6 +942,11 @@
       <c r="H11" s="3" t="inlineStr">
         <is>
           <t>2. 헌법(92점) 교재 및 강의: 박철한 T 해커스 기본강의&amp;심화강의/ 신동욱T 기출문제집&amp; 기출문제강의, OX 문제집/ 김유향 T 최신판례집</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37722&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=88</t>
         </is>
       </c>
     </row>
@@ -927,6 +983,11 @@
           <t>특히, 법 과목은 마지막 한 달전에 꼭 최신 판례와 최신 기출을 보았습니다. 헌법은 최신 기출과 최판이 쏟아져 나오기 때문에 시험 전 마지막 두 달은 시행처별 기출문제를 뽑아 매일 시험치듯이 보았습니다.</t>
         </is>
       </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37280&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="55" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -965,6 +1026,11 @@
           <t>2차과목은 경제학은 김종국 선생님 커리큘럼을 들었습니다. 경제학이 어렵다고 느껴져서 경제학부터 공부를 시작했습니다. 경제학은 문제를 푸는 방법이 비슷하기 때문에 기본적인 원리를 외우고 나서 응용하여 푸는 것을 연습하였습니다. 그리고 기출 회독을 하였고 계산 문제를 시간안에 푸는 연습을 하였습니다. 그리고 시간이 오래결리것 같은 문제보다 빨리 풀리는 문제부터 풀었습니다. 헌법은 황남기 선생님을 들었습니다. 판례문제와 법이론 문제를 나눠서 외웠고 판례는 안외워지는 것 위주로 반복해서 보았습니다. 헌법은 초시때 점수가 안나와서 재시때에는 시간을 많이 투자하였습니다. 행정학은 서현 선생님을 들었습니다. 행정학은 생소한 문제가 계속 출제된다고 생각하여 기출된 주제의 문제는 실수하지 않도록 연습하였고 새로운 주제들은 특강을 들었습니다. 행정법은 황남기 선생님을 들었습니다. 행정법은 판례문제에서 많이 출제된다고 생각하여 판례를 반복하였고 대부분 기출된것에서 출제가 되어 빈출문제를 더 많이 보았습니다.</t>
         </is>
       </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36757&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="55" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1001,6 +1067,11 @@
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>- 행정법: 황남기, 오랜 경험으로 법에 대한 논리구조가 안정되어 있음. 행정법각론은 이론책은 어차피 안 볼 것 같아서, 문제집만 사서 강의들음. 장애직렬은 행정법총론이 잘 되어 있다면 굳이 각론은 안해도 무방할 듯 생각됨. 이론강의, 기출강의, 헌법조문강의 듣으며 기출3회독. 행정법조문강의 운동하면서 수시로 청취함.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36747&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
         </is>
       </c>
     </row>
@@ -1033,6 +1104,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35587&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=125</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="55" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1071,6 +1147,11 @@
           <t>헌법은 신동욱 선생님 강의를 수강하였습니다.헌법 공부의 핵심은 결국 기출 회독이라고 생각합니다.따라서 강의를 수강시 관련 지식을 전부 다 암기한다는 생각보다 해당 법의 취지와 판단근거정도만 파악하고 추후 객관식 공부를 할 때 판례와 법령을 계속적으로 회독하면서 암기하는 것이 중요하다고 판단됩니다. 회계학은 따로 강의를 수강하지 않았습니다.회계학 공부의 핵심은 문제를 유형별로 반복숙달하여 빠르고 정확하게 푸는 것이라고 생각합니다.리스,주식보상비용,유형자산 등등 해당 파트마다 나오는 문제들이 어느정도 정해져 있습니다.따라서 해당 단원별로 빈출 문제들을 빠르고 정확하게 풀수 있게끔 반복숙달하는 것이 중요합니다.결국 객관식 시험은 시간이 부족하기에 정확도도 중요하지만 속도 또한 중요하다고 판단됩니다.</t>
         </is>
       </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41964&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="55" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -1109,6 +1190,11 @@
           <t>*PSAT 언어논리 조윤정 선생님, 자료해석 김용훈 선생님, 상황판단 길규범 선생님 강의 수강하였고, 기본/심화/유형별 문제풀이까지 들었습니다. 특히 선생님들께서 이야기해주신대로 민경채 기출 11년도부터 시간 재면서 다 풀어봤고, 7급 기출도 20년도부터 시간 재면서 다 풀었습니다. 설명도 워낙 자세하게 잘해주시기 때문에 강의만 순서대로 따라간다면 PSAT은 크게 걱정하지 않아도 될 것 같습니다.  *헌법 황남기 선생님 강의 수강하였습니다. 기본이론은 시험을 2번 준비하면서 2번 다 수강하였고 기출강의는 23년 시험 떄와 겹치는게 많아서 23년 수험때만 수강하고 올해는 문제만 풀었습니다. 기본이론 수강 후에 진도에 맞춰서 기출문제 풀면서 1회독 한 후 다시 범위를 나눠서 기본서+기출서 2회독했습니다. 3회독부터는 기본서는 따로 보지 않고 기출서만 반복해서 봤습니다. 기출서는 총 5회독정도 한 것 같습니다. 기출서 회독하시는게 매우 중요하다고 생각하고 선생님이 강조하시는 것처럼 리갈 마인드로 문제를 푸는 것이 아니라 키워드를 기억해서 선지 다 읽지 않고도 바로바로 이게 어떤 판례였는지 기억해서 시간 줄이면서 문제 풀 수 있도록 준비하는 것이 중요한 것 같습니다</t>
         </is>
       </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39641&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="55" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -1145,6 +1231,11 @@
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>- 2차시험이 임박하자 헌법과 행정법이 양이 많아서 기출회독을 더 이상 늘릴 수가 없다고 판단해서 형사소송법과 교정학에 기출회독을 늘리는 전략을 펼쳤지만 아쉽게도 헌법 과목에서 점수가 68점이 나오는 바람에 1점 차이로 불합격을 하였습니다.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36763&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
         </is>
       </c>
     </row>
@@ -1177,6 +1268,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=42079&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="55" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -1215,6 +1311,11 @@
           <t>- 무역실무 (이명호 선생님) 워낙 어떤 문제가 나올지 모르는 과목이기 때문에 기본만 챙기는 것을 추천 드립니다. 각종 협약과 무역이론만 공부하고 나머지 시간은 행정법/헌법에 쏟았습니다. 있는 자료들만 달달 외우고, 기출문제를 N회독 하였습니다.</t>
         </is>
       </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41989&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="55" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -1253,6 +1354,11 @@
           <t>헌법,행정법- 홍대겸 선생님 저는 1년차에 헌법과 행정법 강의를 다른 선생님들의 강의로 수강하였습니다. 그런데 너무나 강의 수도 많고 책도 두꺼워서 공부하기도 어려웠을 뿐만 아니라 내용들을 저의 것으로 만드는 복습 시간이 너무 오래걸려서 공부를 포기하고 싶은 마음이 많이 들었습니다. 하루하루 진도는 나아가는데 모르는 것 투성이에 다음 진도 이해하는데에도 어려움이 있어서 정말 많이 힘들었습니다. 그렇게 첫 해 시험이 끝난 후, 지푸라기라도 잡고 싶은 심정으로 홍대겸 선생님의 강의를 선택하였는데 이 선택이 제가 수험기간중에 했던 가장 좋은 선택이었던 것 같습니다. 우선 책과 강의가 굉장히 컴팩트한 것이 수강생의 심적인 부담을 굉장히 줄여주었습니다. 선생님의 커리큘럼 대로만 따라가더라도 틈틈이 복습하면서 공부를 할 수 있었습니다. 그리고 무엇보다 학생들이 이해하기 쉽도록 예시를 들어주시고, 수업 중간중간에 동기부여가 되는 말씀도 해주시면서 포기하는 마음이 들지 않게끔 학생들을 잘 이끌어주십니다. 1차 시험 이후 2차 전공 시험 전에는 그동안의 내용을 계속해서 까먹지 않게 복습하면서 선생님이 준비해주시는 개인 모의고사를 풀며 마무리한다면 행정법과 헌법에서 크게 어렵</t>
         </is>
       </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41963&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="55" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -1291,6 +1397,11 @@
           <t>행정법 - 홍대겸선생님 커리큘럼 : 기본이론-심화이론-빠른 1회독강의-행정법 법령특강- 행정법 기출문제풀이강의- 행정법 각론 특강 저는 헌법이나 행정법 모두 기본서와 기출문제집을 기준으로 해서 공부했습니다. 따라서 모의고사의 경우에는 모든 수업을 참여하지는 않았고, 시간 감각이나 기출문제의 변형 정도의 느낌만 파악하기 위해 3회 정도씩만 참여하여 감각을 익혔습니다. 물론 시간적인 여유가 있을 경우 모두 참여하시는 것이 당연히 좋지만, 저는 2차 시험 직전까지 회독이 엄청 많이 하지는 못했기 때문에, 모의고사는 감각을 익히는 정도만 참여했습니다. 행정법의 경우에도 헌법과 똑같이 홍대겸 선생님의 강의가 가장 컴팩트하고 이해가 잘 되게끔 설명을 해주시는데에 강점이 있다고 생각합니다. 생소한 법과목을 공부하면서 이해가 뒷받침 되지 않으면 암기도 되지 않고, 뜬구름 잡는 듯한 얘기만 계속해서 듣는 느낌이 들어서 나중에는 머릿 속에서 굉장히 헷갈리는 내용들이 많아집니다. 그러한 과목의 특성들에 맞게 홍대겸 선생님의 강의를 수강하면 불안함을 해소할 수 있고, 선생님이 알려주신 내용들로만으로도 기출문제가 이해되고 해결속도가 빨라지는 것을 몸소 체험할 수 있습니다. 또한 행</t>
         </is>
       </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41962&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="55" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
@@ -1333,6 +1444,11 @@
           <t>기본강의 1회독, 기출문제집 4회독(아이패드에 기록하며 왼쪽위에 네모칸에 틀린문제들 기록), 기본서 회독은 10회독씩 넘어가면서 카운트X, 헌법과 행정법은 기출문제 해설까지 수강, 관세법과 무역학은 기출문제 해설은 패스하고 기본서 회독에 집중. 결국 마지막에 가서는 회독이 가장 중요하다고 생각함. 헌법, 행정법은 최신판례및 기출위주의 회독을 중점적으로 하고 관세법, 무역학의 경우는 문제는 본인의 실력을 체크하는 식으로 활용하면서 기본서를 자세히 꼼꼼하게 암기하는 느낌으로 회독하면 충분히 합격할 수 있다고 생각함.</t>
         </is>
       </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41936&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="55" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -1367,6 +1483,11 @@
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41690&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="55" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
@@ -1405,6 +1526,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39745&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=45</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="55" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -1447,6 +1573,11 @@
           <t>2024년에는 1차 60일 전부터 시작했습니다. 작년에 합격한 경험이 있기에 하루에 한과목씩 모의고사(주로 5급)을 풀었고, 시험 2주전에서야 매일 모의고사를 치거나 온종일 PSAT에 집중했습니다. 시험지 상으로는 언자상 88 88 80이었는데, 마킹실수를 거하게 한 것 같습니다. 언어논리는 실수한 포인트가 기억나는데, 자료해석은 기억이 나지 않습니다. 저처럼 막판에 몰아서 마킹하면 오히려 실수가 날 경우가 크기 때문에 적당히 끊어서 마킹하는 게 좋을 거 같습니다.   [헌법] 강의는 박철한 선생님의 올인원 강의를 듣고 이후 기출문제 풀이로 공부했습니다. 중간에 기출을 아무리 풀어도 이해가 되지 않아 기출인강을 따로 수강했었는데, 이때 크게 점수가 향상되었습니다. 이후 기본서와 기출문제를 계속 반복했고, 시험 한달전에 최신판례 책을 사서 공부했습니다. 최신판례 인강은 2회독을 했고, 따로 책을 3회독한 것 같습니다. 최신판례는 양이 많지 않아 주로 점심을 먹으면서 공부했던 기억이 있습니다. 헌법은 기출이 중요하기에 공기출 사이트에서 올해와 작년에 나온 시험문제를 전부 프린트해서 풀어봤습니다. 그리고 시험 3주 전부터는 기출문제나 모의고사를 풀 때 최대한 모르</t>
         </is>
       </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39651&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="55" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
@@ -1485,6 +1616,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39639&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="55" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -1523,6 +1659,11 @@
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39632&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="55" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
@@ -1561,6 +1702,11 @@
           <t>[관세법] 관세사 수험시절, 이미 공부해봤었기 때문에 자신만만했으나...기출 풀어보면 점수가 잘 나오지 않는 ...과목이었습니다. 관세법 1타 강사 이명호 선생님 기본-심화과정까지 수강했고, 문제풀이는 저 혼자 진행했습니다. 선생님께서는 실제 시험에서 이 부분이 ~이렇게 나온다며 잘 체크해주십니다. 필기해주시는 부분 빠짐없이 다 적어서 외웠습니다. 또 목차노트를 만들었네요. 목차노트를 만들어서 목차옆에 생각나는대로 다 적어주고 맞는지 기본서랑 확인하는 방법으로 공부했습니다. 관세법의 경우 관세직 9급, 7급, 관세사 등 관세법 관련 기출문제 거의 다 뽑아서 풀고, 모르는 선지도 헌법/행정법과 마찬가지로 OX집을 만들어 외웠습니다.</t>
         </is>
       </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36762&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="55" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -1603,6 +1749,11 @@
           <t>9월 : 홍대겸 헌법 하프모의고사, 행정법/헌법 화력집중, 함수민 행정법각론특강, 행정법 문제풀이 특강</t>
         </is>
       </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39642&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="55" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
@@ -1641,6 +1792,11 @@
           <t>2)2차 과목 헌법 황남기T - 경찰간부 준비때부터 들었던 강사님인데 첫단추가 중요한 것을 느꼈습니다. 기반을 잘 다져놓으니 헌법이 효자 과목이었습니다. 특히 시험문제 경향과 예측, 최신 판례 특강이 굉장한 도움이 되었습니다. 기출 무한 회독 하시길 바랍니다. 형법, 형사소송법 김대환T - 경찰에서 유명하셔서 이번에 들었는데 도움이 되었습니다.  행정법 함수민T - 굉장히 열정적으로 어려운 판례도 쉽게 설명해주시고, 카페 질문 글에 답변도 빠르고 친절하게 답해주십니다.</t>
         </is>
       </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41865&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="55" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -1679,6 +1835,11 @@
           <t>2. 전공필기시험    5급을 준비했다보니 7급 국제법과 국제정치학은 꽤나 준비가 되어있던 편이라고 생각했었습니다만, 아니었습니다. 국제법은 그럭저럭 방어가 됐지만, 국제정치학에서 확실히 5급 논술형 시험과 7급 객관식 시험의 차이를 크게 느꼈습니다. 2024년 외무영사직 시험에서 국제법 88점, 국제정치학 56점이라는 점수가 이를 증명하죠. 그리고 헌법도 5급 시험에서처럼 60점 이상만을 목표로 하는 시험이 아니게 되며, 추가적인 공부가 필요해졌습니다. 그래서 이때 해커스 외무영사직 패스를 이용하기로 결정하고, 이상구 선생님과 황남기 선생님를 알게 됐습니다.</t>
         </is>
       </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41922&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="55" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
@@ -1713,6 +1874,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr"/>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41691&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="55" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -1751,6 +1917,11 @@
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41680&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="55" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
@@ -1785,6 +1956,11 @@
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr"/>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39715&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="55" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -1823,6 +1999,11 @@
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39635&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="55" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
@@ -1859,6 +2040,11 @@
       <c r="H37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2차 전공과목 헌법: 신동욱T 기본, 요약, 기출해설, 최신판례 + 신동욱T 기출 1, 2권 회독 반복(홀수번 짝수번 나눠서) + 최신판례 보충 단권화 + 해커스 2차 모의고사 국제정치학: 이상구T 기본, 요약), 기출해설, 동형, 실전모의 + 단권화 + 해커스 2차 모의고사 + 단행본 일부 참조(현대외교정책론(3판), 변환의 세계정치) + 국제기사 수시로 국제법: 이상구T 기본, 요약, 판례, 조약, 기출해설, 동형, 실전모의 + 단권화 + 해커스 2차 모의고사 + 단행본 일부 참조(신국제법강의(12판)) + 판례 정리 후 회독 반복 + 조약 반복 정독 제2외국어를 제외하면, 2차 과목에서 가장  공부하기 수월했던 것은 헌법이었습니다. 모든 직렬이 공통으로 치는 과목이라 정말 많은 기출이 쌓여 있어, 기출만 반복해도 빈출되거나 중요한 판례가 무엇인지 감을 잡을 수 있을 것입니다. 따라서, 다른 2차과목과 달리 개념 강의로는 틀만 대략 잡고, 최대한 빨리 기출문제 회독을 돌리면서 중요 판례를 최대한 많이 보고, 비슷해서 헷갈리는 판례들만 따로 모아 키워드 위주로 별도로 정리할 필요가 있습니다. 또, 3분의 1에서 거의 절반까지도 최신판례가 출제되므로, 시험 </t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37348&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
         </is>
       </c>
     </row>
@@ -1891,6 +2077,11 @@
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35571&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=126</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="55" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
@@ -1929,6 +2120,11 @@
           <t>1. 기본 베이스 서울 4년제 대학 경영학부 재학 중, 회계학 중 재무회계와 원가회계 기초 有, 정부회계 기초 無, 경영학은 전공 기초 수준 베이스 有 헌법과 행정법은 2년 전 검찰직을 준비하면서 공부해본 경험이 있었습니다.</t>
         </is>
       </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39663&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="55" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -1963,6 +2159,11 @@
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36735&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=93</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="55" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
@@ -1999,6 +2200,11 @@
       <c r="H41" s="3" t="inlineStr">
         <is>
           <t>10월부터 기본강의를 듣고 시험 직전에 법령특강, 최신판례특강을 들었습니다. 기본강의를 2배속으로 빠르게 듣고 듣는 중에 기출문제를 바로바로 풀었습니다. 기본강의 끝낸 후에는 기출 회독을 계속 돌렸고, 강의 중에 회독 돌리는 방법을 알려주셔서 시험 한 달 전까지는 계속 기출만 보았으며, 한 달 남았을 때는 법령과 최신판례를 같이 보았습니다. 기출을 많이 보다보면 기본서를 후에 회독 돌릴 때에는 생소한 부분만 보이기 때문에 더 빠르게 회독을 돌릴 수 있었습니다. 황남기 선생님은 특별히 외우는 방법을 알려주시지는 않지만 판례 배경 등을 설명해주셔서 더 기억에 남을 수 있었던 것 같습니다. 또한 비슷한 주제로 위헌, 합헌으로 나뉘는 판례들은 암기하기 위해 따로 노트를 만들었는데 시험 직전에 다시 정리했던 것이 실제 시험장에서 너무 큰 도움이 되었습니다.   (행정법-황남기 선생님, 함수민 선생님) 헌법을 먼저 들었기 때문에 행정법 또한 황남기 선생님을 선택해서 들었습니다. 헌법과 공부방법은 비슷하나 행정법각론 부분은 시험 3달 전에 전년도 강의를 가볍게 황남기 선생님 강의로 듣고 2달 전에는 당해연도 함수민 선생님 강의를 들었고, 시험 한 달 전부터는 각론기출문제</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39681&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
         </is>
       </c>
     </row>
@@ -2035,6 +2241,11 @@
           <t>(행정학) 행정학의 경우에는 대부분의 수험생들이 그렇듯 시험 직전까지도 가장 자신이 없었습니다. 개념의 범위가 너무 넓고 항상 불의타 문제가 나오기 때문에 대비가 어렵다고 느꼈습니다. 행정학의 경우에는 여러 이론들에 대해서 묻기 때문에 이론 간의 비교에 집중하면서 공부하는게 큰 도움이 됐습니다. 간단하게 비유하자면 단순하게 (a 이론의 특성은 키가 작다) 이런 식으로 외우면  혼동이 생길 때가 많습니다. 왜냐하면 a 이론이 b이론과 비교했을 때는 키가 작았지만, 또 다른 c이론과 비교했을 때는 키가 큰 경우가 있기 때문입니다. 행정학은 법 과목의 판례들처럼 딱 정해진 것이 아니어서 어떤 대상과 비교하냐에 따라서 해당 이론의 특성이 아 다르고 어 다르기 때문에  (a 이론은 b 이론과 비교했을 때는 키가 작다) 이런 식으로 유사한 그룹의 개념들끼리 비교를 잡으면서 개념을 유연성 있게 정리하는게 많은 도움이 됐습니다.   (헌법)) 헌법의 경우 처음 기본 강의를 들을 때는 상대적으로 재밌다고 느꼈습니다. 왜냐하면 다양한 판례들이 나오고 아무래도 판례들이 우리 생활과 밀접해 있다 보니 이러한 경우도 있구나 하면서 상대적으로 즐겁게 기본강의를 들었습니다. 하지만 기</t>
         </is>
       </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39640&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="55" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
@@ -2077,6 +2288,11 @@
           <t>2. 헌법(92점) 교재 및 강의: 박철한 T 해커스 기본강의&amp;심화강의/ 신동욱T 기출문제집&amp; 기출문제강의, OX 문제집/ 김유향 T 최신판례집</t>
         </is>
       </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37722&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=88</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="55" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -2115,6 +2331,11 @@
           <t>*PSAT 언어논리 조윤정 선생님, 자료해석 김용훈 선생님, 상황판단 길규범 선생님 강의 수강하였고, 기본/심화/유형별 문제풀이까지 들었습니다. 특히 선생님들께서 이야기해주신대로 민경채 기출 11년도부터 시간 재면서 다 풀어봤고, 7급 기출도 20년도부터 시간 재면서 다 풀었습니다. 설명도 워낙 자세하게 잘해주시기 때문에 강의만 순서대로 따라간다면 PSAT은 크게 걱정하지 않아도 될 것 같습니다.  *헌법 황남기 선생님 강의 수강하였습니다. 기본이론은 시험을 2번 준비하면서 2번 다 수강하였고 기출강의는 23년 시험 떄와 겹치는게 많아서 23년 수험때만 수강하고 올해는 문제만 풀었습니다. 기본이론 수강 후에 진도에 맞춰서 기출문제 풀면서 1회독 한 후 다시 범위를 나눠서 기본서+기출서 2회독했습니다. 3회독부터는 기본서는 따로 보지 않고 기출서만 반복해서 봤습니다. 기출서는 총 5회독정도 한 것 같습니다. 기출서 회독하시는게 매우 중요하다고 생각하고 선생님이 강조하시는 것처럼 리갈 마인드로 문제를 푸는 것이 아니라 키워드를 기억해서 선지 다 읽지 않고도 바로바로 이게 어떤 판례였는지 기억해서 시간 줄이면서 문제 풀 수 있도록 준비하는 것이 중요한 것 같습니다</t>
         </is>
       </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39641&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="55" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
@@ -2153,6 +2374,11 @@
           <t>세무직과 전혀 관련 없는 영어영문학을 전공하였으나 교양과목으로 재무회계와 경제학원론 과목을 수강한 상태였습니다. 회계학 같은 경우 대학교에서 배운 내용이 도움이 되긴 하였으나 경제학은 과목 난이도 때문에 대학교에서 수강할 때에도 어려움을 많이 느꼈던 만큼 수험기간 중에도 큰 벽으로 다가왔습니다. 또한 세법은 과목 특유의 진입장벽 때문에 초반에 이해하기가 굉장히 어려웠습니다. 법과목을 전혀 공부해본 적이 없기 때문에 헌법 또한 혼란스럽기만 했던 것 같습니다. 하지만 해커스 공무원에서 인강을 수강하며 회독을 반복하니 점점 제 것으로 만들 수 있었던 것 같습니다.</t>
         </is>
       </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36750&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="55" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
@@ -2191,6 +2417,11 @@
           <t>- 2차시험이 임박하자 헌법과 행정법이 양이 많아서 기출회독을 더 이상 늘릴 수가 없다고 판단해서 형사소송법과 교정학에 기출회독을 늘리는 전략을 펼쳤지만 아쉽게도 헌법 과목에서 점수가 68점이 나오는 바람에 1점 차이로 불합격을 하였습니다.</t>
         </is>
       </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36763&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="55" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
@@ -2233,6 +2464,11 @@
           <t>기본강의 1회독, 기출문제집 4회독(아이패드에 기록하며 왼쪽위에 네모칸에 틀린문제들 기록), 기본서 회독은 10회독씩 넘어가면서 카운트X, 헌법과 행정법은 기출문제 해설까지 수강, 관세법과 무역학은 기출문제 해설은 패스하고 기본서 회독에 집중. 결국 마지막에 가서는 회독이 가장 중요하다고 생각함. 헌법, 행정법은 최신판례및 기출위주의 회독을 중점적으로 하고 관세법, 무역학의 경우는 문제는 본인의 실력을 체크하는 식으로 활용하면서 기본서를 자세히 꼼꼼하게 암기하는 느낌으로 회독하면 충분히 합격할 수 있다고 생각함.</t>
         </is>
       </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41936&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="55" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
@@ -2267,6 +2503,11 @@
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41690&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="55" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
@@ -2307,6 +2548,11 @@
       <c r="H49" s="3" t="inlineStr">
         <is>
           <t>2024년에는 1차 60일 전부터 시작했습니다. 작년에 합격한 경험이 있기에 하루에 한과목씩 모의고사(주로 5급)을 풀었고, 시험 2주전에서야 매일 모의고사를 치거나 온종일 PSAT에 집중했습니다. 시험지 상으로는 언자상 88 88 80이었는데, 마킹실수를 거하게 한 것 같습니다. 언어논리는 실수한 포인트가 기억나는데, 자료해석은 기억이 나지 않습니다. 저처럼 막판에 몰아서 마킹하면 오히려 실수가 날 경우가 크기 때문에 적당히 끊어서 마킹하는 게 좋을 거 같습니다.   [헌법] 강의는 박철한 선생님의 올인원 강의를 듣고 이후 기출문제 풀이로 공부했습니다. 중간에 기출을 아무리 풀어도 이해가 되지 않아 기출인강을 따로 수강했었는데, 이때 크게 점수가 향상되었습니다. 이후 기본서와 기출문제를 계속 반복했고, 시험 한달전에 최신판례 책을 사서 공부했습니다. 최신판례 인강은 2회독을 했고, 따로 책을 3회독한 것 같습니다. 최신판례는 양이 많지 않아 주로 점심을 먹으면서 공부했던 기억이 있습니다. 헌법은 기출이 중요하기에 공기출 사이트에서 올해와 작년에 나온 시험문제를 전부 프린트해서 풀어봤습니다. 그리고 시험 3주 전부터는 기출문제나 모의고사를 풀 때 최대한 모르</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39651&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
         </is>
       </c>
     </row>
@@ -2343,6 +2589,11 @@
           <t>2-2 헌법헌법은 행정법에 비해 조문문제가 꽤 자주 나오고 단순암기해야할 사항이 많은 과목입니다. 단순암기는 시험끝물에 최대한 외운다고 생각하고 내용상 스토리가 있는 그런부분이 더 외우기 쉽기때문에 이런쪽을 우선 정복하는게 좋다고 생각합니다. 또한 헌법도 최신판례의 비중이 매우 크므로 최신판례 강의를 들으시는것을 추천드립니다.</t>
         </is>
       </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41937&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="55" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
@@ -2377,6 +2628,11 @@
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr"/>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41691&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="55" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -2415,6 +2671,11 @@
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39635&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="55" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
@@ -2451,6 +2712,11 @@
       <c r="H53" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2차 전공과목 헌법: 신동욱T 기본, 요약, 기출해설, 최신판례 + 신동욱T 기출 1, 2권 회독 반복(홀수번 짝수번 나눠서) + 최신판례 보충 단권화 + 해커스 2차 모의고사 국제정치학: 이상구T 기본, 요약), 기출해설, 동형, 실전모의 + 단권화 + 해커스 2차 모의고사 + 단행본 일부 참조(현대외교정책론(3판), 변환의 세계정치) + 국제기사 수시로 국제법: 이상구T 기본, 요약, 판례, 조약, 기출해설, 동형, 실전모의 + 단권화 + 해커스 2차 모의고사 + 단행본 일부 참조(신국제법강의(12판)) + 판례 정리 후 회독 반복 + 조약 반복 정독 제2외국어를 제외하면, 2차 과목에서 가장  공부하기 수월했던 것은 헌법이었습니다. 모든 직렬이 공통으로 치는 과목이라 정말 많은 기출이 쌓여 있어, 기출만 반복해도 빈출되거나 중요한 판례가 무엇인지 감을 잡을 수 있을 것입니다. 따라서, 다른 2차과목과 달리 개념 강의로는 틀만 대략 잡고, 최대한 빨리 기출문제 회독을 돌리면서 중요 판례를 최대한 많이 보고, 비슷해서 헷갈리는 판례들만 따로 모아 키워드 위주로 별도로 정리할 필요가 있습니다. 또, 3분의 1에서 거의 절반까지도 최신판례가 출제되므로, 시험 </t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37348&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
         </is>
       </c>
     </row>
@@ -2483,6 +2749,11 @@
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39664&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="55" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
@@ -2523,6 +2794,11 @@
       <c r="H55" s="3" t="inlineStr">
         <is>
           <t>2024년에는 1차 60일 전부터 시작했습니다. 작년에 합격한 경험이 있기에 하루에 한과목씩 모의고사(주로 5급)을 풀었고, 시험 2주전에서야 매일 모의고사를 치거나 온종일 PSAT에 집중했습니다. 시험지 상으로는 언자상 88 88 80이었는데, 마킹실수를 거하게 한 것 같습니다. 언어논리는 실수한 포인트가 기억나는데, 자료해석은 기억이 나지 않습니다. 저처럼 막판에 몰아서 마킹하면 오히려 실수가 날 경우가 크기 때문에 적당히 끊어서 마킹하는 게 좋을 거 같습니다.   [헌법] 강의는 박철한 선생님의 올인원 강의를 듣고 이후 기출문제 풀이로 공부했습니다. 중간에 기출을 아무리 풀어도 이해가 되지 않아 기출인강을 따로 수강했었는데, 이때 크게 점수가 향상되었습니다. 이후 기본서와 기출문제를 계속 반복했고, 시험 한달전에 최신판례 책을 사서 공부했습니다. 최신판례 인강은 2회독을 했고, 따로 책을 3회독한 것 같습니다. 최신판례는 양이 많지 않아 주로 점심을 먹으면서 공부했던 기억이 있습니다. 헌법은 기출이 중요하기에 공기출 사이트에서 올해와 작년에 나온 시험문제를 전부 프린트해서 풀어봤습니다. 그리고 시험 3주 전부터는 기출문제나 모의고사를 풀 때 최대한 모르</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39651&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
         </is>
       </c>
     </row>
@@ -2559,6 +2835,11 @@
           <t>2-2 헌법헌법은 행정법에 비해 조문문제가 꽤 자주 나오고 단순암기해야할 사항이 많은 과목입니다. 단순암기는 시험끝물에 최대한 외운다고 생각하고 내용상 스토리가 있는 그런부분이 더 외우기 쉽기때문에 이런쪽을 우선 정복하는게 좋다고 생각합니다. 또한 헌법도 최신판례의 비중이 매우 크므로 최신판례 강의를 들으시는것을 추천드립니다.</t>
         </is>
       </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41937&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="55" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
@@ -2595,6 +2876,11 @@
       <c r="H57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2차 전공과목 헌법: 신동욱T 기본, 요약, 기출해설, 최신판례 + 신동욱T 기출 1, 2권 회독 반복(홀수번 짝수번 나눠서) + 최신판례 보충 단권화 + 해커스 2차 모의고사 국제정치학: 이상구T 기본, 요약), 기출해설, 동형, 실전모의 + 단권화 + 해커스 2차 모의고사 + 단행본 일부 참조(현대외교정책론(3판), 변환의 세계정치) + 국제기사 수시로 국제법: 이상구T 기본, 요약, 판례, 조약, 기출해설, 동형, 실전모의 + 단권화 + 해커스 2차 모의고사 + 단행본 일부 참조(신국제법강의(12판)) + 판례 정리 후 회독 반복 + 조약 반복 정독 제2외국어를 제외하면, 2차 과목에서 가장  공부하기 수월했던 것은 헌법이었습니다. 모든 직렬이 공통으로 치는 과목이라 정말 많은 기출이 쌓여 있어, 기출만 반복해도 빈출되거나 중요한 판례가 무엇인지 감을 잡을 수 있을 것입니다. 따라서, 다른 2차과목과 달리 개념 강의로는 틀만 대략 잡고, 최대한 빨리 기출문제 회독을 돌리면서 중요 판례를 최대한 많이 보고, 비슷해서 헷갈리는 판례들만 따로 모아 키워드 위주로 별도로 정리할 필요가 있습니다. 또, 3분의 1에서 거의 절반까지도 최신판례가 출제되므로, 시험 </t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37348&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
         </is>
       </c>
     </row>
@@ -2627,6 +2913,11 @@
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40692&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=31</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="55" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
@@ -2657,6 +2948,11 @@
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr"/>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40688&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=32</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="55" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
@@ -2691,6 +2987,11 @@
           <t>(행정학) 행정학의 경우에는 대부분의 수험생들이 그렇듯 시험 직전까지도 가장 자신이 없었습니다. 개념의 범위가 너무 넓고 항상 불의타 문제가 나오기 때문에 대비가 어렵다고 느꼈습니다. 행정학의 경우에는 여러 이론들에 대해서 묻기 때문에 이론 간의 비교에 집중하면서 공부하는게 큰 도움이 됐습니다. 간단하게 비유하자면 단순하게 (a 이론의 특성은 키가 작다) 이런 식으로 외우면  혼동이 생길 때가 많습니다. 왜냐하면 a 이론이 b이론과 비교했을 때는 키가 작았지만, 또 다른 c이론과 비교했을 때는 키가 큰 경우가 있기 때문입니다. 행정학은 법 과목의 판례들처럼 딱 정해진 것이 아니어서 어떤 대상과 비교하냐에 따라서 해당 이론의 특성이 아 다르고 어 다르기 때문에  (a 이론은 b 이론과 비교했을 때는 키가 작다) 이런 식으로 유사한 그룹의 개념들끼리 비교를 잡으면서 개념을 유연성 있게 정리하는게 많은 도움이 됐습니다.   (헌법)) 헌법의 경우 처음 기본 강의를 들을 때는 상대적으로 재밌다고 느꼈습니다. 왜냐하면 다양한 판례들이 나오고 아무래도 판례들이 우리 생활과 밀접해 있다 보니 이러한 경우도 있구나 하면서 상대적으로 즐겁게 기본강의를 들었습니다. 하지만 기</t>
         </is>
       </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39640&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="55" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
@@ -2733,6 +3034,11 @@
           <t>2. 헌법(92점) 교재 및 강의: 박철한 T 해커스 기본강의&amp;심화강의/ 신동욱T 기출문제집&amp; 기출문제강의, OX 문제집/ 김유향 T 최신판례집</t>
         </is>
       </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37722&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=88</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="55" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -2771,6 +3077,11 @@
           <t>*PSAT 언어논리 조윤정 선생님, 자료해석 김용훈 선생님, 상황판단 길규범 선생님 강의 수강하였고, 기본/심화/유형별 문제풀이까지 들었습니다. 특히 선생님들께서 이야기해주신대로 민경채 기출 11년도부터 시간 재면서 다 풀어봤고, 7급 기출도 20년도부터 시간 재면서 다 풀었습니다. 설명도 워낙 자세하게 잘해주시기 때문에 강의만 순서대로 따라간다면 PSAT은 크게 걱정하지 않아도 될 것 같습니다.  *헌법 황남기 선생님 강의 수강하였습니다. 기본이론은 시험을 2번 준비하면서 2번 다 수강하였고 기출강의는 23년 시험 떄와 겹치는게 많아서 23년 수험때만 수강하고 올해는 문제만 풀었습니다. 기본이론 수강 후에 진도에 맞춰서 기출문제 풀면서 1회독 한 후 다시 범위를 나눠서 기본서+기출서 2회독했습니다. 3회독부터는 기본서는 따로 보지 않고 기출서만 반복해서 봤습니다. 기출서는 총 5회독정도 한 것 같습니다. 기출서 회독하시는게 매우 중요하다고 생각하고 선생님이 강조하시는 것처럼 리갈 마인드로 문제를 푸는 것이 아니라 키워드를 기억해서 선지 다 읽지 않고도 바로바로 이게 어떤 판례였는지 기억해서 시간 줄이면서 문제 풀 수 있도록 준비하는 것이 중요한 것 같습니다</t>
         </is>
       </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39641&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="55" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
@@ -2809,6 +3120,11 @@
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr"/>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39745&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=45</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="55" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
@@ -2847,6 +3163,11 @@
           <t>1. 행정법100 *ㅆㄴ최종모의고사* 이미 국,지9급으로 완성되어 있어서 감만 유지하고 따로 강의를 듣지 않음. 솔직히 초시면 모르겠지만, 재시 또는 재재시라면 ㅆㄴ선생님의 교재사서 기본서의 날개 문제만 돌려서 외워도 충분함. 인강에서 ㅆㄴ선생님도 그렇게 말씀하셨고, 그말 믿고 그렇게 한 결과 3번다 100점 아니면 1개인가 틀렸던 듯함. 가장 핵심은 ㅆㄴ선생님 마무리 모의고사인가 8회짜리 있는데, 그게 정수임. 시간이 너무 없었기 때문에 행정법에 가장 시간을 덜 투자할 수 밖에 없었는데 그래서 기본서 읽을 때도 먼저 날개문제 읽어서 ox하고 틀린 것만 옆에 기본내용 가서 읽고 표시함. 이렇게 틀린 것만 해서 3번 돌림.(근데 초시이신 분들은 기출문제 열심히 돌리셔야함. 기출문제만이 살길입니다. 저는 이미 행정법의 거의 모든 기출문제를 알고 있었고, 잊어버리지 않기 위한 제일 효율적인 방법으로 이렇게 했습니다. 반면 재시거나 재재시이신 분들은 이렇게만 해도 충분함. 그만큼 ㅆㄴ선생님 교재는 완벽하고 믿고가면됨. 솔직히 행정법의 흐름을 아시거나 행정법에 대해서 이해도가 있으시다면 인강 안들어도 됩니다. 교재만 해도 완벽함. 그만큼 해설도 완벽하게 되어있습니다.</t>
         </is>
       </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39671&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="55" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
@@ -2885,6 +3206,11 @@
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr"/>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39639&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="55" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
@@ -2923,6 +3249,11 @@
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39632&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="55" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
@@ -2961,6 +3292,11 @@
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr"/>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36995&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=90</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="55" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
@@ -2999,6 +3335,11 @@
           <t>[관세법] 관세사 수험시절, 이미 공부해봤었기 때문에 자신만만했으나...기출 풀어보면 점수가 잘 나오지 않는 ...과목이었습니다. 관세법 1타 강사 이명호 선생님 기본-심화과정까지 수강했고, 문제풀이는 저 혼자 진행했습니다. 선생님께서는 실제 시험에서 이 부분이 ~이렇게 나온다며 잘 체크해주십니다. 필기해주시는 부분 빠짐없이 다 적어서 외웠습니다. 또 목차노트를 만들었네요. 목차노트를 만들어서 목차옆에 생각나는대로 다 적어주고 맞는지 기본서랑 확인하는 방법으로 공부했습니다. 관세법의 경우 관세직 9급, 7급, 관세사 등 관세법 관련 기출문제 거의 다 뽑아서 풀고, 모르는 선지도 헌법/행정법과 마찬가지로 OX집을 만들어 외웠습니다.</t>
         </is>
       </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36762&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="55" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
@@ -3039,6 +3380,11 @@
       <c r="H69" s="3" t="inlineStr">
         <is>
           <t>9월 : 홍대겸 헌법 하프모의고사, 행정법/헌법 화력집중, 함수민 행정법각론특강, 행정법 문제풀이 특강</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39642&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
         </is>
       </c>
     </row>
@@ -3075,6 +3421,11 @@
           <t>2-2 헌법헌법은 행정법에 비해 조문문제가 꽤 자주 나오고 단순암기해야할 사항이 많은 과목입니다. 단순암기는 시험끝물에 최대한 외운다고 생각하고 내용상 스토리가 있는 그런부분이 더 외우기 쉽기때문에 이런쪽을 우선 정복하는게 좋다고 생각합니다. 또한 헌법도 최신판례의 비중이 매우 크므로 최신판례 강의를 들으시는것을 추천드립니다.</t>
         </is>
       </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41937&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="55" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
@@ -3117,6 +3468,11 @@
           <t>공부기간: 2025년 3월~ 2025년 9월  한국사와 영어는 따둔 상황이었고 제2외국어는 올해 5월에 취득하였습니다(대학 전공이라 어려움은 없었습니다). 전공과목들의 베이스가 하나도 없어서 외무영사직 해커스 0원 패스를 구매해서 수험생활을 시작하였습니다. 국제법, 국제정치학은 이상구 선생님, 헌법은 홍대겸 선생님 강의를 수강하였습니다. 공부는 하루에 7~8시간 정도를 했고 주에 2일은 열심히 노는데 집중하였습니다. 8월 중순부터는 쉬는 날 없이 8시간 정도 계속 하였습니다. 끝나고 나니 중간중간 잘 놀고 잘 쉬었던 것이 수험생활에서 멘탈관리에 많은 도움이 되었던 것 같습니다.  1. 1차 PSAT 96/100/92  저는 처음 PSAT 문제들을 풀어봤을때 크게 어렵지 않을 것 같다고 느껴서 강의는 수강하지 않았습니다. 1차 시험 한달 반 전부터 5급 문제들을 20문제씩 60분동안 푸는 연습을 하였고, 실전에서는 긴장이 많이 될 것 같아서 어느 상황에서든지 문제를 풀 수 있는는게 가장 중요하다고 생각을 하였고, 일부러 시끄러운 카페나 새로운 환경, 가장 피곤할때, 도서관에 도착하자마자 등 가장 집중이 되는 때에 60분동안 풀어보는 연습을 계속 했습니다. 시험</t>
         </is>
       </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41711&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="55" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
@@ -3151,6 +3507,11 @@
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41691&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="55" customHeight="1">
       <c r="A73" s="3" t="inlineStr">
@@ -3185,6 +3546,11 @@
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr"/>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39715&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="55" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
@@ -3223,6 +3589,11 @@
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39635&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="55" customHeight="1">
       <c r="A75" s="3" t="inlineStr">
@@ -3257,6 +3628,11 @@
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr"/>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41696&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="55" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
@@ -3295,6 +3671,11 @@
           <t>10월부터 기본강의를 듣고 시험 직전에 법령특강, 최신판례특강을 들었습니다. 기본강의를 2배속으로 빠르게 듣고 듣는 중에 기출문제를 바로바로 풀었습니다. 기본강의 끝낸 후에는 기출 회독을 계속 돌렸고, 강의 중에 회독 돌리는 방법을 알려주셔서 시험 한 달 전까지는 계속 기출만 보았으며, 한 달 남았을 때는 법령과 최신판례를 같이 보았습니다. 기출을 많이 보다보면 기본서를 후에 회독 돌릴 때에는 생소한 부분만 보이기 때문에 더 빠르게 회독을 돌릴 수 있었습니다. 황남기 선생님은 특별히 외우는 방법을 알려주시지는 않지만 판례 배경 등을 설명해주셔서 더 기억에 남을 수 있었던 것 같습니다. 또한 비슷한 주제로 위헌, 합헌으로 나뉘는 판례들은 암기하기 위해 따로 노트를 만들었는데 시험 직전에 다시 정리했던 것이 실제 시험장에서 너무 큰 도움이 되었습니다.   (행정법-황남기 선생님, 함수민 선생님) 헌법을 먼저 들었기 때문에 행정법 또한 황남기 선생님을 선택해서 들었습니다. 헌법과 공부방법은 비슷하나 행정법각론 부분은 시험 3달 전에 전년도 강의를 가볍게 황남기 선생님 강의로 듣고 2달 전에는 당해연도 함수민 선생님 강의를 들었고, 시험 한 달 전부터는 각론기출문제</t>
         </is>
       </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39681&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="55" customHeight="1">
       <c r="A77" s="3" t="inlineStr">
@@ -3337,6 +3718,11 @@
           <t>(2) 헌법 [강의] 황남기쌤 헌법 기본이론 23년, 24년 각 1회 수강 [교재] 황남기쌤 기본서 3회독(인강 수강 포함) [교재] 황남기쌤 기출문제집 9회독 [교재] 경간 소간 국회직 등등 각종 시행처 최신기출</t>
         </is>
       </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39626&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="55" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
@@ -3375,6 +3761,11 @@
           <t>*PSAT 언어논리 조윤정 선생님, 자료해석 김용훈 선생님, 상황판단 길규범 선생님 강의 수강하였고, 기본/심화/유형별 문제풀이까지 들었습니다. 특히 선생님들께서 이야기해주신대로 민경채 기출 11년도부터 시간 재면서 다 풀어봤고, 7급 기출도 20년도부터 시간 재면서 다 풀었습니다. 설명도 워낙 자세하게 잘해주시기 때문에 강의만 순서대로 따라간다면 PSAT은 크게 걱정하지 않아도 될 것 같습니다.  *헌법 황남기 선생님 강의 수강하였습니다. 기본이론은 시험을 2번 준비하면서 2번 다 수강하였고 기출강의는 23년 시험 떄와 겹치는게 많아서 23년 수험때만 수강하고 올해는 문제만 풀었습니다. 기본이론 수강 후에 진도에 맞춰서 기출문제 풀면서 1회독 한 후 다시 범위를 나눠서 기본서+기출서 2회독했습니다. 3회독부터는 기본서는 따로 보지 않고 기출서만 반복해서 봤습니다. 기출서는 총 5회독정도 한 것 같습니다. 기출서 회독하시는게 매우 중요하다고 생각하고 선생님이 강조하시는 것처럼 리갈 마인드로 문제를 푸는 것이 아니라 키워드를 기억해서 선지 다 읽지 않고도 바로바로 이게 어떤 판례였는지 기억해서 시간 줄이면서 문제 풀 수 있도록 준비하는 것이 중요한 것 같습니다</t>
         </is>
       </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39641&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="55" customHeight="1">
       <c r="A79" s="3" t="inlineStr">
@@ -3413,6 +3804,11 @@
           <t>헌법,행정법- 홍대겸 선생님 저는 1년차에 헌법과 행정법 강의를 다른 선생님들의 강의로 수강하였습니다. 그런데 너무나 강의 수도 많고 책도 두꺼워서 공부하기도 어려웠을 뿐만 아니라 내용들을 저의 것으로 만드는 복습 시간이 너무 오래걸려서 공부를 포기하고 싶은 마음이 많이 들었습니다. 하루하루 진도는 나아가는데 모르는 것 투성이에 다음 진도 이해하는데에도 어려움이 있어서 정말 많이 힘들었습니다. 그렇게 첫 해 시험이 끝난 후, 지푸라기라도 잡고 싶은 심정으로 홍대겸 선생님의 강의를 선택하였는데 이 선택이 제가 수험기간중에 했던 가장 좋은 선택이었던 것 같습니다. 우선 책과 강의가 굉장히 컴팩트한 것이 수강생의 심적인 부담을 굉장히 줄여주었습니다. 선생님의 커리큘럼 대로만 따라가더라도 틈틈이 복습하면서 공부를 할 수 있었습니다. 그리고 무엇보다 학생들이 이해하기 쉽도록 예시를 들어주시고, 수업 중간중간에 동기부여가 되는 말씀도 해주시면서 포기하는 마음이 들지 않게끔 학생들을 잘 이끌어주십니다. 1차 시험 이후 2차 전공 시험 전에는 그동안의 내용을 계속해서 까먹지 않게 복습하면서 선생님이 준비해주시는 개인 모의고사를 풀며 마무리한다면 행정법과 헌법에서 크게 어렵</t>
         </is>
       </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41963&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="55" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
@@ -3455,6 +3851,11 @@
           <t>기본강의 1회독, 기출문제집 4회독(아이패드에 기록하며 왼쪽위에 네모칸에 틀린문제들 기록), 기본서 회독은 10회독씩 넘어가면서 카운트X, 헌법과 행정법은 기출문제 해설까지 수강, 관세법과 무역학은 기출문제 해설은 패스하고 기본서 회독에 집중. 결국 마지막에 가서는 회독이 가장 중요하다고 생각함. 헌법, 행정법은 최신판례및 기출위주의 회독을 중점적으로 하고 관세법, 무역학의 경우는 문제는 본인의 실력을 체크하는 식으로 활용하면서 기본서를 자세히 꼼꼼하게 암기하는 느낌으로 회독하면 충분히 합격할 수 있다고 생각함.</t>
         </is>
       </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41936&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="55" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
@@ -3489,6 +3890,11 @@
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr"/>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41690&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="55" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
@@ -3531,6 +3937,11 @@
           <t>2024년에는 1차 60일 전부터 시작했습니다. 작년에 합격한 경험이 있기에 하루에 한과목씩 모의고사(주로 5급)을 풀었고, 시험 2주전에서야 매일 모의고사를 치거나 온종일 PSAT에 집중했습니다. 시험지 상으로는 언자상 88 88 80이었는데, 마킹실수를 거하게 한 것 같습니다. 언어논리는 실수한 포인트가 기억나는데, 자료해석은 기억이 나지 않습니다. 저처럼 막판에 몰아서 마킹하면 오히려 실수가 날 경우가 크기 때문에 적당히 끊어서 마킹하는 게 좋을 거 같습니다.   [헌법] 강의는 박철한 선생님의 올인원 강의를 듣고 이후 기출문제 풀이로 공부했습니다. 중간에 기출을 아무리 풀어도 이해가 되지 않아 기출인강을 따로 수강했었는데, 이때 크게 점수가 향상되었습니다. 이후 기본서와 기출문제를 계속 반복했고, 시험 한달전에 최신판례 책을 사서 공부했습니다. 최신판례 인강은 2회독을 했고, 따로 책을 3회독한 것 같습니다. 최신판례는 양이 많지 않아 주로 점심을 먹으면서 공부했던 기억이 있습니다. 헌법은 기출이 중요하기에 공기출 사이트에서 올해와 작년에 나온 시험문제를 전부 프린트해서 풀어봤습니다. 그리고 시험 3주 전부터는 기출문제나 모의고사를 풀 때 최대한 모르</t>
         </is>
       </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39651&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="55" customHeight="1">
       <c r="A83" s="3" t="inlineStr">
@@ -3573,6 +3984,11 @@
           <t>공부기간: 2025년 3월~ 2025년 9월  한국사와 영어는 따둔 상황이었고 제2외국어는 올해 5월에 취득하였습니다(대학 전공이라 어려움은 없었습니다). 전공과목들의 베이스가 하나도 없어서 외무영사직 해커스 0원 패스를 구매해서 수험생활을 시작하였습니다. 국제법, 국제정치학은 이상구 선생님, 헌법은 홍대겸 선생님 강의를 수강하였습니다. 공부는 하루에 7~8시간 정도를 했고 주에 2일은 열심히 노는데 집중하였습니다. 8월 중순부터는 쉬는 날 없이 8시간 정도 계속 하였습니다. 끝나고 나니 중간중간 잘 놀고 잘 쉬었던 것이 수험생활에서 멘탈관리에 많은 도움이 되었던 것 같습니다.  1. 1차 PSAT 96/100/92  저는 처음 PSAT 문제들을 풀어봤을때 크게 어렵지 않을 것 같다고 느껴서 강의는 수강하지 않았습니다. 1차 시험 한달 반 전부터 5급 문제들을 20문제씩 60분동안 푸는 연습을 하였고, 실전에서는 긴장이 많이 될 것 같아서 어느 상황에서든지 문제를 풀 수 있는는게 가장 중요하다고 생각을 하였고, 일부러 시끄러운 카페나 새로운 환경, 가장 피곤할때, 도서관에 도착하자마자 등 가장 집중이 되는 때에 60분동안 풀어보는 연습을 계속 했습니다. 시험</t>
         </is>
       </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41711&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="55" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
@@ -3611,6 +4027,11 @@
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41680&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="55" customHeight="1">
       <c r="A85" s="3" t="inlineStr">
@@ -3641,6 +4062,11 @@
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr"/>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41486&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=5</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="55" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
@@ -3677,6 +4103,11 @@
       <c r="H86" s="2" t="inlineStr">
         <is>
           <t>10월부터 기본강의를 듣고 시험 직전에 법령특강, 최신판례특강을 들었습니다. 기본강의를 2배속으로 빠르게 듣고 듣는 중에 기출문제를 바로바로 풀었습니다. 기본강의 끝낸 후에는 기출 회독을 계속 돌렸고, 강의 중에 회독 돌리는 방법을 알려주셔서 시험 한 달 전까지는 계속 기출만 보았으며, 한 달 남았을 때는 법령과 최신판례를 같이 보았습니다. 기출을 많이 보다보면 기본서를 후에 회독 돌릴 때에는 생소한 부분만 보이기 때문에 더 빠르게 회독을 돌릴 수 있었습니다. 황남기 선생님은 특별히 외우는 방법을 알려주시지는 않지만 판례 배경 등을 설명해주셔서 더 기억에 남을 수 있었던 것 같습니다. 또한 비슷한 주제로 위헌, 합헌으로 나뉘는 판례들은 암기하기 위해 따로 노트를 만들었는데 시험 직전에 다시 정리했던 것이 실제 시험장에서 너무 큰 도움이 되었습니다.   (행정법-황남기 선생님, 함수민 선생님) 헌법을 먼저 들었기 때문에 행정법 또한 황남기 선생님을 선택해서 들었습니다. 헌법과 공부방법은 비슷하나 행정법각론 부분은 시험 3달 전에 전년도 강의를 가볍게 황남기 선생님 강의로 듣고 2달 전에는 당해연도 함수민 선생님 강의를 들었고, 시험 한 달 전부터는 각론기출문제</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39681&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
         </is>
       </c>
     </row>
@@ -3709,6 +4140,11 @@
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr"/>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39664&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="55" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
@@ -3747,6 +4183,11 @@
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39745&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=45</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="55" customHeight="1">
       <c r="A89" s="3" t="inlineStr">
@@ -3785,6 +4226,11 @@
           <t>2. 전공필기시험    5급을 준비했다보니 7급 국제법과 국제정치학은 꽤나 준비가 되어있던 편이라고 생각했었습니다만, 아니었습니다. 국제법은 그럭저럭 방어가 됐지만, 국제정치학에서 확실히 5급 논술형 시험과 7급 객관식 시험의 차이를 크게 느꼈습니다. 2024년 외무영사직 시험에서 국제법 88점, 국제정치학 56점이라는 점수가 이를 증명하죠. 그리고 헌법도 5급 시험에서처럼 60점 이상만을 목표로 하는 시험이 아니게 되며, 추가적인 공부가 필요해졌습니다. 그래서 이때 해커스 외무영사직 패스를 이용하기로 결정하고, 이상구 선생님과 황남기 선생님를 알게 됐습니다.</t>
         </is>
       </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41922&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="55" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
@@ -3827,6 +4273,11 @@
           <t>공부기간: 2025년 3월~ 2025년 9월  한국사와 영어는 따둔 상황이었고 제2외국어는 올해 5월에 취득하였습니다(대학 전공이라 어려움은 없었습니다). 전공과목들의 베이스가 하나도 없어서 외무영사직 해커스 0원 패스를 구매해서 수험생활을 시작하였습니다. 국제법, 국제정치학은 이상구 선생님, 헌법은 홍대겸 선생님 강의를 수강하였습니다. 공부는 하루에 7~8시간 정도를 했고 주에 2일은 열심히 노는데 집중하였습니다. 8월 중순부터는 쉬는 날 없이 8시간 정도 계속 하였습니다. 끝나고 나니 중간중간 잘 놀고 잘 쉬었던 것이 수험생활에서 멘탈관리에 많은 도움이 되었던 것 같습니다.  1. 1차 PSAT 96/100/92  저는 처음 PSAT 문제들을 풀어봤을때 크게 어렵지 않을 것 같다고 느껴서 강의는 수강하지 않았습니다. 1차 시험 한달 반 전부터 5급 문제들을 20문제씩 60분동안 푸는 연습을 하였고, 실전에서는 긴장이 많이 될 것 같아서 어느 상황에서든지 문제를 풀 수 있는는게 가장 중요하다고 생각을 하였고, 일부러 시끄러운 카페나 새로운 환경, 가장 피곤할때, 도서관에 도착하자마자 등 가장 집중이 되는 때에 60분동안 풀어보는 연습을 계속 했습니다. 시험</t>
         </is>
       </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41711&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="55" customHeight="1">
       <c r="A91" s="3" t="inlineStr">
@@ -3863,6 +4314,11 @@
       <c r="H91" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2차 전공과목 헌법: 신동욱T 기본, 요약, 기출해설, 최신판례 + 신동욱T 기출 1, 2권 회독 반복(홀수번 짝수번 나눠서) + 최신판례 보충 단권화 + 해커스 2차 모의고사 국제정치학: 이상구T 기본, 요약), 기출해설, 동형, 실전모의 + 단권화 + 해커스 2차 모의고사 + 단행본 일부 참조(현대외교정책론(3판), 변환의 세계정치) + 국제기사 수시로 국제법: 이상구T 기본, 요약, 판례, 조약, 기출해설, 동형, 실전모의 + 단권화 + 해커스 2차 모의고사 + 단행본 일부 참조(신국제법강의(12판)) + 판례 정리 후 회독 반복 + 조약 반복 정독 제2외국어를 제외하면, 2차 과목에서 가장  공부하기 수월했던 것은 헌법이었습니다. 모든 직렬이 공통으로 치는 과목이라 정말 많은 기출이 쌓여 있어, 기출만 반복해도 빈출되거나 중요한 판례가 무엇인지 감을 잡을 수 있을 것입니다. 따라서, 다른 2차과목과 달리 개념 강의로는 틀만 대략 잡고, 최대한 빨리 기출문제 회독을 돌리면서 중요 판례를 최대한 많이 보고, 비슷해서 헷갈리는 판례들만 따로 모아 키워드 위주로 별도로 정리할 필요가 있습니다. 또, 3분의 1에서 거의 절반까지도 최신판례가 출제되므로, 시험 </t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37348&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
         </is>
       </c>
     </row>
@@ -3899,6 +4355,11 @@
           <t>3. 나의 수험 계획표 다양한 방법들을 시도해보았지만, 저는 앞서 말했던 것처럼 하루에 4과목을 전부 보는 방식이 저에게 잘 맞아서 그렇게 진행했습니다. 우선 공부는 8시 이전에 열품타 착석스터디를 통해 스스로를 컨트롤 하며 시작했습니다. 행정학 2시간(이때 말하는 시간은 최소 시간입니다. 인강이나 문풀 상황에 따라 10-15분 정도는 더 진행할 때가 많습니다) -&gt; 행정법 1시간 -&gt; 약 12시쯤 점심식사 및 식곤증을 물리치기 위한 샤워 등 재정비 -&gt; 2시 쯤. 경제학 2시간 (그나마 손을 가장 많이 써서 덜 졸려서 이걸 이때 했습니다) -&gt; 1시간 정도 행정법 추가 공부 -&gt; 6시쯤 저녁 식사 후 휴식 -&gt; 2시간 동안 헌법 마무리</t>
         </is>
       </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41729&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="55" customHeight="1">
       <c r="A93" s="3" t="inlineStr">
@@ -3935,6 +4396,11 @@
       <c r="H93" s="3" t="inlineStr">
         <is>
           <t>1) 4월~6월 : 기본 이론 강의 수강 행정법, 헌법 (홍대겸)/ 행정학 (서현) 기본 강의를 수강하였습니다. 두 분을 선택한 계기는 좀 불순한데, 일단 교재가 없어도 수업을 들을 수 있게 판서 혹은 PPT를 활용하는 수업방식이 마음에 들었습니다. 불순한 계기와 달리, 결과적으로 두 분을 선택하여서 좋은 결과를 얻을 수 있었습니다. 홍대겸 선생님의 가장 큰 장점이자 매력은 컴팩트함입니다. 법학을 이해하는 데 필요한 기본적인 논리는 놓치지 않고 설명해주시되 디테일을 과감하게 생략하며 빠르게 진도를 나가시는 타입이십니다. 그래서 강의 회차와 시간 모두 짧습니다. 가볍고 빠르게 나아가는 수업은 빠르게 기본 이론을 배우고 싶었던 당시의 저에게는 최고의 선택이었습니다. 설명도 가능한 직관적이고 단정적으로 하셔서 법학이 까다롭고 어렵다는 선입견을 깨시고 부담을 많이 덜어주셨습니다. "빠른 1회독" 강의도 큰 도움이 되었습니다. 기초 이론을 가볍게 맛본 수험생을 대상으로 하는 강의인데, 기초 강의 때는 생략하였던 변칙적인 판례를 설명해주시기도 하고, 말 그대로 빠르게 행정법 전체를 복습할 수 있습니다. 서현 선생님의 장점은 체계성입니다. 그동안의 기출 경향을 모두 꿰고</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41687&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
         </is>
       </c>
     </row>
@@ -3967,6 +4433,11 @@
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41368&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=10</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="55" customHeight="1">
       <c r="A95" s="3" t="inlineStr">
@@ -3997,6 +4468,11 @@
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr"/>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39633&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="55" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
@@ -4027,6 +4503,11 @@
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39340&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=49</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="55" customHeight="1">
       <c r="A97" s="3" t="inlineStr">
@@ -4061,6 +4542,11 @@
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr"/>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37336&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="55" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
@@ -4091,6 +4577,11 @@
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37288&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="55" customHeight="1">
       <c r="A99" s="3" t="inlineStr">
@@ -4127,6 +4618,11 @@
       <c r="H99" s="3" t="inlineStr">
         <is>
           <t>헌법&amp;행정법은 황남기 선생님 강의 들으면서 기본서 위주보다는 기출을 계속 무한으로 돌렸습니다.</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37101&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=90</t>
         </is>
       </c>
     </row>
@@ -4159,6 +4655,11 @@
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36908&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="55" customHeight="1">
       <c r="A101" s="3" t="inlineStr">
@@ -4193,6 +4694,11 @@
           <t>안녕하세요. 처음 공무원 준비를 시작할 때에는 저의 계획이 정말 실현될 수 있을지 저 스스로도 의심하게 되고 막막하였지만 결국 제가 올해 합격을 하게 되었습니다. 저는 단기 합격을 위한 계획을 세웠습니다(5개월 정도). 과정을 이야기하자면, 먼저 저는 1월 말 정도부터 5급 1차 시험을 준비하였습니다. 피셋 공부와 헌법 1회독을 이 시기에 처음 하게 되었습니다. 하지만 1차 시험에서 떨어졌고, 그 충격으로 5월 8일까지 공부를 안하고 놀기만 했습니다. 어버이날이 지나고 더는 부모님께 손벌리기가 싫었고, 사기업에 종사하는 것보다는 국가를 위한 일을 하고자 하는 마음이 있었기 때문에 7급 공무원을 준비하게 되었습니다(진짜입니다). 다행히 1차 시험은 1월에 5급 시험을 준비했던 경험으로 4일 정도 공부하여 붙을 수 있었습니다. 이후 2차 시험을 위해 제가 먼저 준비를 시작했던 과목은 경제학이었습니다. 아무래도 이해가 필요한 과목이고 휘발성이 다른 암기과목들에 비해 낮다고 생각을 하였기 때문에 가장 먼저 준비를 했습니다. 경제학은 일단 처음 들을 때에는 당연히 이해가 잘 안되지만 저는 이해를 해야 넘어가는 스타일이라 조금 까다로웠습니다. 김종국 선생님의 강의를 들</t>
         </is>
       </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36756&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="55" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
@@ -4227,6 +4733,11 @@
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36754&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="55" customHeight="1">
       <c r="A103" s="3" t="inlineStr">
@@ -4265,6 +4776,11 @@
           <t>- 헌법 : 신동욱 선생님 공시 진입하려고 헌법 기본서를 주문해 놓고 뜨악했더랬죠, 이 두꺼운 책을 머릿속에 우겨넣을 생각을 하니 공무원 준비를 괜히 했나 생각이 들 정도였습니다. 하지만 선생님 강의 천천히 따라가니 결국엔 큰 흐름이 잡혀요. 왜 사람들이 헌법 회독이 중요하다. 회독회독 그렇게 얘기하는지 처음엔 몰랐는데애초에 1300쪽 가까이 되는 이 방대한 분량을 하나하나 꼼꼼히 이해하면서 다른과목 하듯이 진도나간다는게 욕심이었습니다. 팁 드리자면 처음 1회차는 강의 틀어놓고 책정리하면서, 흐름 (대충 이런게 있구나) 느끼는데 집중하고</t>
         </is>
       </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36748&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="55" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
@@ -4299,6 +4815,11 @@
       </c>
       <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=34959&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=140</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="55" customHeight="1">
       <c r="A105" s="3" t="inlineStr">
@@ -4333,6 +4854,11 @@
         </is>
       </c>
       <c r="H105" s="3" t="inlineStr"/>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39729&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="55" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
@@ -4367,6 +4893,11 @@
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39634&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="55" customHeight="1">
       <c r="A107" s="3" t="inlineStr">
@@ -4405,6 +4936,11 @@
           <t>-헌법 지역인재7급을 위한 헌법 강의는 따로 마련된 것이 없었기 때문에 저는 신동욱 선생님의 법원직 헌법 강의를 수강하였습니다. 법쪽으로 전혀 지식이 없는 상태라 입문특강부터 차근차근 수강하였는데, 신동욱 선생님께서 입문특강에서 정말 잘 설명해주셔서 헌법에 대한 기초 지식뿐만 아니라 관심도가 많이 상승했던 것 같습니다. 기본이론을 들으면서도 많은 판례들과 함께 설명해주셔서 각 판례들의 구체적인 스토리를 들으며 재밌게 공부하였던 것 같습니다. 헌법 노베이스이신 분들께 신동욱 선생님의 헌법 강의 강추 드립니다!</t>
         </is>
       </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=34803&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=141</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="55" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
@@ -4445,6 +4981,11 @@
       <c r="H108" s="2" t="inlineStr">
         <is>
           <t>-헌법 지역인재7급을 위한 헌법 강의는 따로 마련된 것이 없었기 때문에 저는 신동욱 선생님의 법원직 헌법 강의를 수강하였습니다. 법쪽으로 전혀 지식이 없는 상태라 입문특강부터 차근차근 수강하였는데, 신동욱 선생님께서 입문특강에서 정말 잘 설명해주셔서 헌법에 대한 기초 지식뿐만 아니라 관심도가 많이 상승했던 것 같습니다. 기본이론을 들으면서도 많은 판례들과 함께 설명해주셔서 각 판례들의 구체적인 스토리를 들으며 재밌게 공부하였던 것 같습니다. 헌법 노베이스이신 분들께 신동욱 선생님의 헌법 강의 강추 드립니다!</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=34802&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=141</t>
         </is>
       </c>
     </row>
@@ -4481,6 +5022,11 @@
           <t>1차 피셋은 작년 합격 경험이 있어서 7월부터 시작하였고 6월까지는 2차과목 위주로 공부하였습니다. 하루를 9-12시, 13-17시, 18-22시로 3등분 하여 헌법, 행정법, 관세법을 공부하였습니다.</t>
         </is>
       </c>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39769&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=45</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="55" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
@@ -4519,6 +5065,11 @@
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39739&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=45</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="55" customHeight="1">
       <c r="A111" s="3" t="inlineStr">
@@ -4553,6 +5104,11 @@
         </is>
       </c>
       <c r="H111" s="3" t="inlineStr"/>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39623&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="55" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
@@ -4589,6 +5145,11 @@
       <c r="H112" s="2" t="inlineStr">
         <is>
           <t>- 헌법: 헌법은 제가 제일 재미있게 공부한 과목이었습니다. 맨 처음 교재가 배송되어 왔을 때는 그 엄청난 책 두께에 잠시 주눅이 들었었지만, 강의를 들으며 차근차근 따라나가고 판례를 반복해서 읽다보면 어느새 진도가 쭉 나가있더라구요. 저는 신동욱 선생님의 강의를 들었습니다. 신동욱 선생님은 차분하게 강의를 진행하시면서도 중간중간 위트 있는 농담으로 강의가 지루하지 않게 해주셔서 너무 좋았습니다. 커리큘럼 자체도 깔끔하기 때문에 신동욱 선생님의 강의를 들으면서 판례를 중심으로 복습을 꾸준히 해준다면 큰 무리없이 헌법 고득점이 가능할 것 같습니다. 특히 선생님의 최신판례특강은 꼭 듣는 것을 추천합니다.</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39652&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
         </is>
       </c>
     </row>
@@ -4621,6 +5182,11 @@
         </is>
       </c>
       <c r="H113" s="3" t="inlineStr"/>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=34832&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=141</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="55" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
@@ -4657,6 +5223,11 @@
       <c r="H114" s="2" t="inlineStr">
         <is>
           <t>- 헌법과 아주 유사하게 인강 수강 후 당일 2회독 확보, 다음날까지 3회독 확보하는 식으로 학습</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39802&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=45</t>
         </is>
       </c>
     </row>
@@ -4693,6 +5264,11 @@
           <t>그래서 다른 전공과목은 뒷전에 두고 피셋을 열심히 준비했었는데, 제 생각에는 이때 많이 올려둔 피셋 실력 덕에 1차는 매년 합격할 수 있었던 것 같습니다. 처음에는 외영직 프리패스에 포함되어 있는 조은정, 김용훈, 길규범 선생님의 강의를 커리 순서대로 다 따라가며 듣고, 개인적으로 5급 기출을 여러번 풀었습니다. 헌법은 제가 가장 많은 노력을 투자했는데도 가장 낮은 점수를 받은 과목입니다. 헌법을 유난히 어려워하는건 제가 조금 특이 케이스 인 것 같긴 하지만, 혹시나 저 같은 수험생분들은 자신에게 맞는 강사님을 찾는 것이 중요하기 때문에 여러 강사님들의 시범강의나 무료제공 강의들을 한 번씩 들어보고 결정해보시는 것도 괜찮을 것 같습니다.</t>
         </is>
       </c>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39646&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="55" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
@@ -4733,6 +5309,11 @@
       <c r="H116" s="2" t="inlineStr">
         <is>
           <t>-헌법도 초시 때 기본 강의 듣고 후로는 강의 안 듣고 혼자 학습, 이 때 교재: 간추린 로스쿨 핵심강의 헌법</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39628&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
         </is>
       </c>
     </row>
@@ -4765,6 +5346,11 @@
         </is>
       </c>
       <c r="H117" s="3" t="inlineStr"/>
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36759&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="55" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
@@ -4795,6 +5381,11 @@
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr"/>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38613&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=71</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="55" customHeight="1">
       <c r="A119" s="3" t="inlineStr">
@@ -4829,6 +5420,11 @@
         </is>
       </c>
       <c r="H119" s="3" t="inlineStr"/>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35581&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=126</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="55" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
@@ -4863,6 +5459,11 @@
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr"/>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35554&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=126</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="55" customHeight="1">
       <c r="A121" s="3" t="inlineStr">
@@ -4901,9 +5502,14 @@
         </is>
       </c>
       <c r="H121" s="3" t="inlineStr"/>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39644&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H121"/>
+  <autoFilter ref="A1:I121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4914,7 +5520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4925,6 +5531,7 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -4968,6 +5575,11 @@
           <t>발췌문2</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -5002,6 +5614,11 @@
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41696&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="55" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -5032,6 +5649,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40692&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=31</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="55" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -5062,6 +5684,11 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40688&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=32</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="55" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -5100,6 +5727,11 @@
           <t>10월부터 기본강의를 듣고 시험 직전에 법령특강, 최신판례특강을 들었습니다. 기본강의를 2배속으로 빠르게 듣고 듣는 중에 기출문제를 바로바로 풀었습니다. 기본강의 끝낸 후에는 기출 회독을 계속 돌렸고, 강의 중에 회독 돌리는 방법을 알려주셔서 시험 한 달 전까지는 계속 기출만 보았으며, 한 달 남았을 때는 법령과 최신판례를 같이 보았습니다. 기출을 많이 보다보면 기본서를 후에 회독 돌릴 때에는 생소한 부분만 보이기 때문에 더 빠르게 회독을 돌릴 수 있었습니다. 황남기 선생님은 특별히 외우는 방법을 알려주시지는 않지만 판례 배경 등을 설명해주셔서 더 기억에 남을 수 있었던 것 같습니다. 또한 비슷한 주제로 위헌, 합헌으로 나뉘는 판례들은 암기하기 위해 따로 노트를 만들었는데 시험 직전에 다시 정리했던 것이 실제 시험장에서 너무 큰 도움이 되었습니다.   (행정법-황남기 선생님, 함수민 선생님) 헌법을 먼저 들었기 때문에 행정법 또한 황남기 선생님을 선택해서 들었습니다. 헌법과 공부방법은 비슷하나 행정법각론 부분은 시험 3달 전에 전년도 강의를 가볍게 황남기 선생님 강의로 듣고 2달 전에는 당해연도 함수민 선생님 강의를 들었고, 시험 한 달 전부터는 각론기출문제</t>
         </is>
       </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39681&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -5138,6 +5770,11 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39662&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="55" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -5172,6 +5809,11 @@
           <t>(행정학) 행정학의 경우에는 대부분의 수험생들이 그렇듯 시험 직전까지도 가장 자신이 없었습니다. 개념의 범위가 너무 넓고 항상 불의타 문제가 나오기 때문에 대비가 어렵다고 느꼈습니다. 행정학의 경우에는 여러 이론들에 대해서 묻기 때문에 이론 간의 비교에 집중하면서 공부하는게 큰 도움이 됐습니다. 간단하게 비유하자면 단순하게 (a 이론의 특성은 키가 작다) 이런 식으로 외우면  혼동이 생길 때가 많습니다. 왜냐하면 a 이론이 b이론과 비교했을 때는 키가 작았지만, 또 다른 c이론과 비교했을 때는 키가 큰 경우가 있기 때문입니다. 행정학은 법 과목의 판례들처럼 딱 정해진 것이 아니어서 어떤 대상과 비교하냐에 따라서 해당 이론의 특성이 아 다르고 어 다르기 때문에  (a 이론은 b 이론과 비교했을 때는 키가 작다) 이런 식으로 유사한 그룹의 개념들끼리 비교를 잡으면서 개념을 유연성 있게 정리하는게 많은 도움이 됐습니다.   (헌법)) 헌법의 경우 처음 기본 강의를 들을 때는 상대적으로 재밌다고 느꼈습니다. 왜냐하면 다양한 판례들이 나오고 아무래도 판례들이 우리 생활과 밀접해 있다 보니 이러한 경우도 있구나 하면서 상대적으로 즐겁게 기본강의를 들었습니다. 하지만 기</t>
         </is>
       </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39640&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="55" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -5214,6 +5856,11 @@
           <t>(2) 헌법 [강의] 황남기쌤 헌법 기본이론 23년, 24년 각 1회 수강 [교재] 황남기쌤 기본서 3회독(인강 수강 포함) [교재] 황남기쌤 기출문제집 9회독 [교재] 경간 소간 국회직 등등 각종 시행처 최신기출</t>
         </is>
       </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39626&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="55" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -5248,6 +5895,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39624&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="55" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -5290,6 +5942,11 @@
           <t>2차 과목 헌법 - 신동욱 스마트헌법 기출문제풀이 행정법 - 함수민 쉬운 행정법 기출문제풀이 행정학 - 송상호 명품 행정학 단원별 문제풀이, 신경향 흐름의 주요테마 및 단원별 문제풀이 경제학 - 김종국 국(局) 경제학 기본이론, 심화이론, 7급 기출문제풀이, 국회직 기출문제풀이 모의고사 - 해커스공무원 2024 대비 제9회 7급 합격예측 모의고사</t>
         </is>
       </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39621&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="55" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -5330,6 +5987,11 @@
       <c r="H11" s="3" t="inlineStr">
         <is>
           <t>2. 헌법(92점) 교재 및 강의: 박철한 T 해커스 기본강의&amp;심화강의/ 신동욱T 기출문제집&amp; 기출문제강의, OX 문제집/ 김유향 T 최신판례집</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37722&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=88</t>
         </is>
       </c>
     </row>
@@ -5366,6 +6028,11 @@
           <t>특히, 법 과목은 마지막 한 달전에 꼭 최신 판례와 최신 기출을 보았습니다. 헌법은 최신 기출과 최판이 쏟아져 나오기 때문에 시험 전 마지막 두 달은 시행처별 기출문제를 뽑아 매일 시험치듯이 보았습니다.</t>
         </is>
       </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37280&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="55" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -5404,6 +6071,11 @@
           <t>2차과목은 경제학은 김종국 선생님 커리큘럼을 들었습니다. 경제학이 어렵다고 느껴져서 경제학부터 공부를 시작했습니다. 경제학은 문제를 푸는 방법이 비슷하기 때문에 기본적인 원리를 외우고 나서 응용하여 푸는 것을 연습하였습니다. 그리고 기출 회독을 하였고 계산 문제를 시간안에 푸는 연습을 하였습니다. 그리고 시간이 오래결리것 같은 문제보다 빨리 풀리는 문제부터 풀었습니다. 헌법은 황남기 선생님을 들었습니다. 판례문제와 법이론 문제를 나눠서 외웠고 판례는 안외워지는 것 위주로 반복해서 보았습니다. 헌법은 초시때 점수가 안나와서 재시때에는 시간을 많이 투자하였습니다. 행정학은 서현 선생님을 들었습니다. 행정학은 생소한 문제가 계속 출제된다고 생각하여 기출된 주제의 문제는 실수하지 않도록 연습하였고 새로운 주제들은 특강을 들었습니다. 행정법은 황남기 선생님을 들었습니다. 행정법은 판례문제에서 많이 출제된다고 생각하여 판례를 반복하였고 대부분 기출된것에서 출제가 되어 빈출문제를 더 많이 보았습니다.</t>
         </is>
       </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36757&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="55" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -5440,6 +6112,11 @@
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>- 행정법: 황남기, 오랜 경험으로 법에 대한 논리구조가 안정되어 있음. 행정법각론은 이론책은 어차피 안 볼 것 같아서, 문제집만 사서 강의들음. 장애직렬은 행정법총론이 잘 되어 있다면 굳이 각론은 안해도 무방할 듯 생각됨. 이론강의, 기출강의, 헌법조문강의 듣으며 기출3회독. 행정법조문강의 운동하면서 수시로 청취함.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36747&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
         </is>
       </c>
     </row>
@@ -5472,6 +6149,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35587&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=125</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="55" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -5510,6 +6192,11 @@
           <t>헌법은 신동욱 선생님 강의를 수강하였습니다.헌법 공부의 핵심은 결국 기출 회독이라고 생각합니다.따라서 강의를 수강시 관련 지식을 전부 다 암기한다는 생각보다 해당 법의 취지와 판단근거정도만 파악하고 추후 객관식 공부를 할 때 판례와 법령을 계속적으로 회독하면서 암기하는 것이 중요하다고 판단됩니다. 회계학은 따로 강의를 수강하지 않았습니다.회계학 공부의 핵심은 문제를 유형별로 반복숙달하여 빠르고 정확하게 푸는 것이라고 생각합니다.리스,주식보상비용,유형자산 등등 해당 파트마다 나오는 문제들이 어느정도 정해져 있습니다.따라서 해당 단원별로 빈출 문제들을 빠르고 정확하게 풀수 있게끔 반복숙달하는 것이 중요합니다.결국 객관식 시험은 시간이 부족하기에 정확도도 중요하지만 속도 또한 중요하다고 판단됩니다.</t>
         </is>
       </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41964&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="55" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -5548,6 +6235,11 @@
           <t>*PSAT 언어논리 조윤정 선생님, 자료해석 김용훈 선생님, 상황판단 길규범 선생님 강의 수강하였고, 기본/심화/유형별 문제풀이까지 들었습니다. 특히 선생님들께서 이야기해주신대로 민경채 기출 11년도부터 시간 재면서 다 풀어봤고, 7급 기출도 20년도부터 시간 재면서 다 풀었습니다. 설명도 워낙 자세하게 잘해주시기 때문에 강의만 순서대로 따라간다면 PSAT은 크게 걱정하지 않아도 될 것 같습니다.  *헌법 황남기 선생님 강의 수강하였습니다. 기본이론은 시험을 2번 준비하면서 2번 다 수강하였고 기출강의는 23년 시험 떄와 겹치는게 많아서 23년 수험때만 수강하고 올해는 문제만 풀었습니다. 기본이론 수강 후에 진도에 맞춰서 기출문제 풀면서 1회독 한 후 다시 범위를 나눠서 기본서+기출서 2회독했습니다. 3회독부터는 기본서는 따로 보지 않고 기출서만 반복해서 봤습니다. 기출서는 총 5회독정도 한 것 같습니다. 기출서 회독하시는게 매우 중요하다고 생각하고 선생님이 강조하시는 것처럼 리갈 마인드로 문제를 푸는 것이 아니라 키워드를 기억해서 선지 다 읽지 않고도 바로바로 이게 어떤 판례였는지 기억해서 시간 줄이면서 문제 풀 수 있도록 준비하는 것이 중요한 것 같습니다</t>
         </is>
       </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39641&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="55" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -5584,6 +6276,11 @@
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>- 2차시험이 임박하자 헌법과 행정법이 양이 많아서 기출회독을 더 이상 늘릴 수가 없다고 판단해서 형사소송법과 교정학에 기출회독을 늘리는 전략을 펼쳤지만 아쉽게도 헌법 과목에서 점수가 68점이 나오는 바람에 1점 차이로 불합격을 하였습니다.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36763&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
         </is>
       </c>
     </row>
@@ -5616,6 +6313,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=42079&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="55" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -5654,6 +6356,11 @@
           <t>- 무역실무 (이명호 선생님) 워낙 어떤 문제가 나올지 모르는 과목이기 때문에 기본만 챙기는 것을 추천 드립니다. 각종 협약과 무역이론만 공부하고 나머지 시간은 행정법/헌법에 쏟았습니다. 있는 자료들만 달달 외우고, 기출문제를 N회독 하였습니다.</t>
         </is>
       </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41989&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="55" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -5692,6 +6399,11 @@
           <t>헌법,행정법- 홍대겸 선생님 저는 1년차에 헌법과 행정법 강의를 다른 선생님들의 강의로 수강하였습니다. 그런데 너무나 강의 수도 많고 책도 두꺼워서 공부하기도 어려웠을 뿐만 아니라 내용들을 저의 것으로 만드는 복습 시간이 너무 오래걸려서 공부를 포기하고 싶은 마음이 많이 들었습니다. 하루하루 진도는 나아가는데 모르는 것 투성이에 다음 진도 이해하는데에도 어려움이 있어서 정말 많이 힘들었습니다. 그렇게 첫 해 시험이 끝난 후, 지푸라기라도 잡고 싶은 심정으로 홍대겸 선생님의 강의를 선택하였는데 이 선택이 제가 수험기간중에 했던 가장 좋은 선택이었던 것 같습니다. 우선 책과 강의가 굉장히 컴팩트한 것이 수강생의 심적인 부담을 굉장히 줄여주었습니다. 선생님의 커리큘럼 대로만 따라가더라도 틈틈이 복습하면서 공부를 할 수 있었습니다. 그리고 무엇보다 학생들이 이해하기 쉽도록 예시를 들어주시고, 수업 중간중간에 동기부여가 되는 말씀도 해주시면서 포기하는 마음이 들지 않게끔 학생들을 잘 이끌어주십니다. 1차 시험 이후 2차 전공 시험 전에는 그동안의 내용을 계속해서 까먹지 않게 복습하면서 선생님이 준비해주시는 개인 모의고사를 풀며 마무리한다면 행정법과 헌법에서 크게 어렵</t>
         </is>
       </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41963&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="55" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -5730,6 +6442,11 @@
           <t>행정법 - 홍대겸선생님 커리큘럼 : 기본이론-심화이론-빠른 1회독강의-행정법 법령특강- 행정법 기출문제풀이강의- 행정법 각론 특강 저는 헌법이나 행정법 모두 기본서와 기출문제집을 기준으로 해서 공부했습니다. 따라서 모의고사의 경우에는 모든 수업을 참여하지는 않았고, 시간 감각이나 기출문제의 변형 정도의 느낌만 파악하기 위해 3회 정도씩만 참여하여 감각을 익혔습니다. 물론 시간적인 여유가 있을 경우 모두 참여하시는 것이 당연히 좋지만, 저는 2차 시험 직전까지 회독이 엄청 많이 하지는 못했기 때문에, 모의고사는 감각을 익히는 정도만 참여했습니다. 행정법의 경우에도 헌법과 똑같이 홍대겸 선생님의 강의가 가장 컴팩트하고 이해가 잘 되게끔 설명을 해주시는데에 강점이 있다고 생각합니다. 생소한 법과목을 공부하면서 이해가 뒷받침 되지 않으면 암기도 되지 않고, 뜬구름 잡는 듯한 얘기만 계속해서 듣는 느낌이 들어서 나중에는 머릿 속에서 굉장히 헷갈리는 내용들이 많아집니다. 그러한 과목의 특성들에 맞게 홍대겸 선생님의 강의를 수강하면 불안함을 해소할 수 있고, 선생님이 알려주신 내용들로만으로도 기출문제가 이해되고 해결속도가 빨라지는 것을 몸소 체험할 수 있습니다. 또한 행</t>
         </is>
       </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41962&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="55" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
@@ -5772,6 +6489,11 @@
           <t>기본강의 1회독, 기출문제집 4회독(아이패드에 기록하며 왼쪽위에 네모칸에 틀린문제들 기록), 기본서 회독은 10회독씩 넘어가면서 카운트X, 헌법과 행정법은 기출문제 해설까지 수강, 관세법과 무역학은 기출문제 해설은 패스하고 기본서 회독에 집중. 결국 마지막에 가서는 회독이 가장 중요하다고 생각함. 헌법, 행정법은 최신판례및 기출위주의 회독을 중점적으로 하고 관세법, 무역학의 경우는 문제는 본인의 실력을 체크하는 식으로 활용하면서 기본서를 자세히 꼼꼼하게 암기하는 느낌으로 회독하면 충분히 합격할 수 있다고 생각함.</t>
         </is>
       </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41936&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="55" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -5806,6 +6528,11 @@
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41690&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="55" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
@@ -5844,6 +6571,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39745&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=45</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="55" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -5886,6 +6618,11 @@
           <t>2024년에는 1차 60일 전부터 시작했습니다. 작년에 합격한 경험이 있기에 하루에 한과목씩 모의고사(주로 5급)을 풀었고, 시험 2주전에서야 매일 모의고사를 치거나 온종일 PSAT에 집중했습니다. 시험지 상으로는 언자상 88 88 80이었는데, 마킹실수를 거하게 한 것 같습니다. 언어논리는 실수한 포인트가 기억나는데, 자료해석은 기억이 나지 않습니다. 저처럼 막판에 몰아서 마킹하면 오히려 실수가 날 경우가 크기 때문에 적당히 끊어서 마킹하는 게 좋을 거 같습니다.   [헌법] 강의는 박철한 선생님의 올인원 강의를 듣고 이후 기출문제 풀이로 공부했습니다. 중간에 기출을 아무리 풀어도 이해가 되지 않아 기출인강을 따로 수강했었는데, 이때 크게 점수가 향상되었습니다. 이후 기본서와 기출문제를 계속 반복했고, 시험 한달전에 최신판례 책을 사서 공부했습니다. 최신판례 인강은 2회독을 했고, 따로 책을 3회독한 것 같습니다. 최신판례는 양이 많지 않아 주로 점심을 먹으면서 공부했던 기억이 있습니다. 헌법은 기출이 중요하기에 공기출 사이트에서 올해와 작년에 나온 시험문제를 전부 프린트해서 풀어봤습니다. 그리고 시험 3주 전부터는 기출문제나 모의고사를 풀 때 최대한 모르</t>
         </is>
       </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39651&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="55" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
@@ -5924,6 +6661,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39639&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="55" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -5962,6 +6704,11 @@
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39632&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="55" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
@@ -6000,6 +6747,11 @@
           <t>[관세법] 관세사 수험시절, 이미 공부해봤었기 때문에 자신만만했으나...기출 풀어보면 점수가 잘 나오지 않는 ...과목이었습니다. 관세법 1타 강사 이명호 선생님 기본-심화과정까지 수강했고, 문제풀이는 저 혼자 진행했습니다. 선생님께서는 실제 시험에서 이 부분이 ~이렇게 나온다며 잘 체크해주십니다. 필기해주시는 부분 빠짐없이 다 적어서 외웠습니다. 또 목차노트를 만들었네요. 목차노트를 만들어서 목차옆에 생각나는대로 다 적어주고 맞는지 기본서랑 확인하는 방법으로 공부했습니다. 관세법의 경우 관세직 9급, 7급, 관세사 등 관세법 관련 기출문제 거의 다 뽑아서 풀고, 모르는 선지도 헌법/행정법과 마찬가지로 OX집을 만들어 외웠습니다.</t>
         </is>
       </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36762&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="55" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -6042,6 +6794,11 @@
           <t>9월 : 홍대겸 헌법 하프모의고사, 행정법/헌법 화력집중, 함수민 행정법각론특강, 행정법 문제풀이 특강</t>
         </is>
       </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39642&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="55" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
@@ -6080,6 +6837,11 @@
           <t>2)2차 과목 헌법 황남기T - 경찰간부 준비때부터 들었던 강사님인데 첫단추가 중요한 것을 느꼈습니다. 기반을 잘 다져놓으니 헌법이 효자 과목이었습니다. 특히 시험문제 경향과 예측, 최신 판례 특강이 굉장한 도움이 되었습니다. 기출 무한 회독 하시길 바랍니다. 형법, 형사소송법 김대환T - 경찰에서 유명하셔서 이번에 들었는데 도움이 되었습니다.  행정법 함수민T - 굉장히 열정적으로 어려운 판례도 쉽게 설명해주시고, 카페 질문 글에 답변도 빠르고 친절하게 답해주십니다.</t>
         </is>
       </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41865&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="55" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -6118,6 +6880,11 @@
           <t>2. 전공필기시험    5급을 준비했다보니 7급 국제법과 국제정치학은 꽤나 준비가 되어있던 편이라고 생각했었습니다만, 아니었습니다. 국제법은 그럭저럭 방어가 됐지만, 국제정치학에서 확실히 5급 논술형 시험과 7급 객관식 시험의 차이를 크게 느꼈습니다. 2024년 외무영사직 시험에서 국제법 88점, 국제정치학 56점이라는 점수가 이를 증명하죠. 그리고 헌법도 5급 시험에서처럼 60점 이상만을 목표로 하는 시험이 아니게 되며, 추가적인 공부가 필요해졌습니다. 그래서 이때 해커스 외무영사직 패스를 이용하기로 결정하고, 이상구 선생님과 황남기 선생님를 알게 됐습니다.</t>
         </is>
       </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41922&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="55" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
@@ -6152,6 +6919,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr"/>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41691&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="55" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -6190,6 +6962,11 @@
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41680&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="55" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
@@ -6224,6 +7001,11 @@
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr"/>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39715&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="55" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -6262,6 +7044,11 @@
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39635&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="55" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
@@ -6298,6 +7085,11 @@
       <c r="H37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2차 전공과목 헌법: 신동욱T 기본, 요약, 기출해설, 최신판례 + 신동욱T 기출 1, 2권 회독 반복(홀수번 짝수번 나눠서) + 최신판례 보충 단권화 + 해커스 2차 모의고사 국제정치학: 이상구T 기본, 요약), 기출해설, 동형, 실전모의 + 단권화 + 해커스 2차 모의고사 + 단행본 일부 참조(현대외교정책론(3판), 변환의 세계정치) + 국제기사 수시로 국제법: 이상구T 기본, 요약, 판례, 조약, 기출해설, 동형, 실전모의 + 단권화 + 해커스 2차 모의고사 + 단행본 일부 참조(신국제법강의(12판)) + 판례 정리 후 회독 반복 + 조약 반복 정독 제2외국어를 제외하면, 2차 과목에서 가장  공부하기 수월했던 것은 헌법이었습니다. 모든 직렬이 공통으로 치는 과목이라 정말 많은 기출이 쌓여 있어, 기출만 반복해도 빈출되거나 중요한 판례가 무엇인지 감을 잡을 수 있을 것입니다. 따라서, 다른 2차과목과 달리 개념 강의로는 틀만 대략 잡고, 최대한 빨리 기출문제 회독을 돌리면서 중요 판례를 최대한 많이 보고, 비슷해서 헷갈리는 판례들만 따로 모아 키워드 위주로 별도로 정리할 필요가 있습니다. 또, 3분의 1에서 거의 절반까지도 최신판례가 출제되므로, 시험 </t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37348&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
         </is>
       </c>
     </row>
@@ -6330,6 +7122,11 @@
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35571&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=126</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="55" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
@@ -6368,6 +7165,11 @@
           <t>1. 기본 베이스 서울 4년제 대학 경영학부 재학 중, 회계학 중 재무회계와 원가회계 기초 有, 정부회계 기초 無, 경영학은 전공 기초 수준 베이스 有 헌법과 행정법은 2년 전 검찰직을 준비하면서 공부해본 경험이 있었습니다.</t>
         </is>
       </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39663&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="55" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -6402,9 +7204,14 @@
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36735&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=93</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H40"/>
+  <autoFilter ref="A1:I40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6415,7 +7222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6426,6 +7233,7 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -6469,6 +7277,11 @@
           <t>발췌문2</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -6505,6 +7318,11 @@
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>10월부터 기본강의를 듣고 시험 직전에 법령특강, 최신판례특강을 들었습니다. 기본강의를 2배속으로 빠르게 듣고 듣는 중에 기출문제를 바로바로 풀었습니다. 기본강의 끝낸 후에는 기출 회독을 계속 돌렸고, 강의 중에 회독 돌리는 방법을 알려주셔서 시험 한 달 전까지는 계속 기출만 보았으며, 한 달 남았을 때는 법령과 최신판례를 같이 보았습니다. 기출을 많이 보다보면 기본서를 후에 회독 돌릴 때에는 생소한 부분만 보이기 때문에 더 빠르게 회독을 돌릴 수 있었습니다. 황남기 선생님은 특별히 외우는 방법을 알려주시지는 않지만 판례 배경 등을 설명해주셔서 더 기억에 남을 수 있었던 것 같습니다. 또한 비슷한 주제로 위헌, 합헌으로 나뉘는 판례들은 암기하기 위해 따로 노트를 만들었는데 시험 직전에 다시 정리했던 것이 실제 시험장에서 너무 큰 도움이 되었습니다.   (행정법-황남기 선생님, 함수민 선생님) 헌법을 먼저 들었기 때문에 행정법 또한 황남기 선생님을 선택해서 들었습니다. 헌법과 공부방법은 비슷하나 행정법각론 부분은 시험 3달 전에 전년도 강의를 가볍게 황남기 선생님 강의로 듣고 2달 전에는 당해연도 함수민 선생님 강의를 들었고, 시험 한 달 전부터는 각론기출문제</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39681&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
         </is>
       </c>
     </row>
@@ -6541,6 +7359,11 @@
           <t>(행정학) 행정학의 경우에는 대부분의 수험생들이 그렇듯 시험 직전까지도 가장 자신이 없었습니다. 개념의 범위가 너무 넓고 항상 불의타 문제가 나오기 때문에 대비가 어렵다고 느꼈습니다. 행정학의 경우에는 여러 이론들에 대해서 묻기 때문에 이론 간의 비교에 집중하면서 공부하는게 큰 도움이 됐습니다. 간단하게 비유하자면 단순하게 (a 이론의 특성은 키가 작다) 이런 식으로 외우면  혼동이 생길 때가 많습니다. 왜냐하면 a 이론이 b이론과 비교했을 때는 키가 작았지만, 또 다른 c이론과 비교했을 때는 키가 큰 경우가 있기 때문입니다. 행정학은 법 과목의 판례들처럼 딱 정해진 것이 아니어서 어떤 대상과 비교하냐에 따라서 해당 이론의 특성이 아 다르고 어 다르기 때문에  (a 이론은 b 이론과 비교했을 때는 키가 작다) 이런 식으로 유사한 그룹의 개념들끼리 비교를 잡으면서 개념을 유연성 있게 정리하는게 많은 도움이 됐습니다.   (헌법)) 헌법의 경우 처음 기본 강의를 들을 때는 상대적으로 재밌다고 느꼈습니다. 왜냐하면 다양한 판례들이 나오고 아무래도 판례들이 우리 생활과 밀접해 있다 보니 이러한 경우도 있구나 하면서 상대적으로 즐겁게 기본강의를 들었습니다. 하지만 기</t>
         </is>
       </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39640&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="55" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -6583,6 +7406,11 @@
           <t>2. 헌법(92점) 교재 및 강의: 박철한 T 해커스 기본강의&amp;심화강의/ 신동욱T 기출문제집&amp; 기출문제강의, OX 문제집/ 김유향 T 최신판례집</t>
         </is>
       </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37722&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=88</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="55" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -6621,6 +7449,11 @@
           <t>*PSAT 언어논리 조윤정 선생님, 자료해석 김용훈 선생님, 상황판단 길규범 선생님 강의 수강하였고, 기본/심화/유형별 문제풀이까지 들었습니다. 특히 선생님들께서 이야기해주신대로 민경채 기출 11년도부터 시간 재면서 다 풀어봤고, 7급 기출도 20년도부터 시간 재면서 다 풀었습니다. 설명도 워낙 자세하게 잘해주시기 때문에 강의만 순서대로 따라간다면 PSAT은 크게 걱정하지 않아도 될 것 같습니다.  *헌법 황남기 선생님 강의 수강하였습니다. 기본이론은 시험을 2번 준비하면서 2번 다 수강하였고 기출강의는 23년 시험 떄와 겹치는게 많아서 23년 수험때만 수강하고 올해는 문제만 풀었습니다. 기본이론 수강 후에 진도에 맞춰서 기출문제 풀면서 1회독 한 후 다시 범위를 나눠서 기본서+기출서 2회독했습니다. 3회독부터는 기본서는 따로 보지 않고 기출서만 반복해서 봤습니다. 기출서는 총 5회독정도 한 것 같습니다. 기출서 회독하시는게 매우 중요하다고 생각하고 선생님이 강조하시는 것처럼 리갈 마인드로 문제를 푸는 것이 아니라 키워드를 기억해서 선지 다 읽지 않고도 바로바로 이게 어떤 판례였는지 기억해서 시간 줄이면서 문제 풀 수 있도록 준비하는 것이 중요한 것 같습니다</t>
         </is>
       </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39641&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -6659,6 +7492,11 @@
           <t>세무직과 전혀 관련 없는 영어영문학을 전공하였으나 교양과목으로 재무회계와 경제학원론 과목을 수강한 상태였습니다. 회계학 같은 경우 대학교에서 배운 내용이 도움이 되긴 하였으나 경제학은 과목 난이도 때문에 대학교에서 수강할 때에도 어려움을 많이 느꼈던 만큼 수험기간 중에도 큰 벽으로 다가왔습니다. 또한 세법은 과목 특유의 진입장벽 때문에 초반에 이해하기가 굉장히 어려웠습니다. 법과목을 전혀 공부해본 적이 없기 때문에 헌법 또한 혼란스럽기만 했던 것 같습니다. 하지만 해커스 공무원에서 인강을 수강하며 회독을 반복하니 점점 제 것으로 만들 수 있었던 것 같습니다.</t>
         </is>
       </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36750&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="55" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -6697,6 +7535,11 @@
           <t>- 2차시험이 임박하자 헌법과 행정법이 양이 많아서 기출회독을 더 이상 늘릴 수가 없다고 판단해서 형사소송법과 교정학에 기출회독을 늘리는 전략을 펼쳤지만 아쉽게도 헌법 과목에서 점수가 68점이 나오는 바람에 1점 차이로 불합격을 하였습니다.</t>
         </is>
       </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36763&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="55" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -6739,6 +7582,11 @@
           <t>기본강의 1회독, 기출문제집 4회독(아이패드에 기록하며 왼쪽위에 네모칸에 틀린문제들 기록), 기본서 회독은 10회독씩 넘어가면서 카운트X, 헌법과 행정법은 기출문제 해설까지 수강, 관세법과 무역학은 기출문제 해설은 패스하고 기본서 회독에 집중. 결국 마지막에 가서는 회독이 가장 중요하다고 생각함. 헌법, 행정법은 최신판례및 기출위주의 회독을 중점적으로 하고 관세법, 무역학의 경우는 문제는 본인의 실력을 체크하는 식으로 활용하면서 기본서를 자세히 꼼꼼하게 암기하는 느낌으로 회독하면 충분히 합격할 수 있다고 생각함.</t>
         </is>
       </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41936&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="55" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -6773,6 +7621,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41690&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="55" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -6813,6 +7666,11 @@
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2024년에는 1차 60일 전부터 시작했습니다. 작년에 합격한 경험이 있기에 하루에 한과목씩 모의고사(주로 5급)을 풀었고, 시험 2주전에서야 매일 모의고사를 치거나 온종일 PSAT에 집중했습니다. 시험지 상으로는 언자상 88 88 80이었는데, 마킹실수를 거하게 한 것 같습니다. 언어논리는 실수한 포인트가 기억나는데, 자료해석은 기억이 나지 않습니다. 저처럼 막판에 몰아서 마킹하면 오히려 실수가 날 경우가 크기 때문에 적당히 끊어서 마킹하는 게 좋을 거 같습니다.   [헌법] 강의는 박철한 선생님의 올인원 강의를 듣고 이후 기출문제 풀이로 공부했습니다. 중간에 기출을 아무리 풀어도 이해가 되지 않아 기출인강을 따로 수강했었는데, 이때 크게 점수가 향상되었습니다. 이후 기본서와 기출문제를 계속 반복했고, 시험 한달전에 최신판례 책을 사서 공부했습니다. 최신판례 인강은 2회독을 했고, 따로 책을 3회독한 것 같습니다. 최신판례는 양이 많지 않아 주로 점심을 먹으면서 공부했던 기억이 있습니다. 헌법은 기출이 중요하기에 공기출 사이트에서 올해와 작년에 나온 시험문제를 전부 프린트해서 풀어봤습니다. 그리고 시험 3주 전부터는 기출문제나 모의고사를 풀 때 최대한 모르</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39651&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
         </is>
       </c>
     </row>
@@ -6849,6 +7707,11 @@
           <t>2-2 헌법헌법은 행정법에 비해 조문문제가 꽤 자주 나오고 단순암기해야할 사항이 많은 과목입니다. 단순암기는 시험끝물에 최대한 외운다고 생각하고 내용상 스토리가 있는 그런부분이 더 외우기 쉽기때문에 이런쪽을 우선 정복하는게 좋다고 생각합니다. 또한 헌법도 최신판례의 비중이 매우 크므로 최신판례 강의를 들으시는것을 추천드립니다.</t>
         </is>
       </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41937&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="55" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -6883,6 +7746,11 @@
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41691&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="55" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -6921,6 +7789,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39635&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="55" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -6959,9 +7832,14 @@
           <t xml:space="preserve">2차 전공과목 헌법: 신동욱T 기본, 요약, 기출해설, 최신판례 + 신동욱T 기출 1, 2권 회독 반복(홀수번 짝수번 나눠서) + 최신판례 보충 단권화 + 해커스 2차 모의고사 국제정치학: 이상구T 기본, 요약), 기출해설, 동형, 실전모의 + 단권화 + 해커스 2차 모의고사 + 단행본 일부 참조(현대외교정책론(3판), 변환의 세계정치) + 국제기사 수시로 국제법: 이상구T 기본, 요약, 판례, 조약, 기출해설, 동형, 실전모의 + 단권화 + 해커스 2차 모의고사 + 단행본 일부 참조(신국제법강의(12판)) + 판례 정리 후 회독 반복 + 조약 반복 정독 제2외국어를 제외하면, 2차 과목에서 가장  공부하기 수월했던 것은 헌법이었습니다. 모든 직렬이 공통으로 치는 과목이라 정말 많은 기출이 쌓여 있어, 기출만 반복해도 빈출되거나 중요한 판례가 무엇인지 감을 잡을 수 있을 것입니다. 따라서, 다른 2차과목과 달리 개념 강의로는 틀만 대략 잡고, 최대한 빨리 기출문제 회독을 돌리면서 중요 판례를 최대한 많이 보고, 비슷해서 헷갈리는 판례들만 따로 모아 키워드 위주로 별도로 정리할 필요가 있습니다. 또, 3분의 1에서 거의 절반까지도 최신판례가 출제되므로, 시험 </t>
         </is>
       </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37348&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H14"/>
+  <autoFilter ref="A1:I14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6972,7 +7850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6983,6 +7861,7 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -7026,6 +7905,11 @@
           <t>발췌문2</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -7056,6 +7940,11 @@
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39664&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="55" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -7096,6 +7985,11 @@
       <c r="H3" s="3" t="inlineStr">
         <is>
           <t>2024년에는 1차 60일 전부터 시작했습니다. 작년에 합격한 경험이 있기에 하루에 한과목씩 모의고사(주로 5급)을 풀었고, 시험 2주전에서야 매일 모의고사를 치거나 온종일 PSAT에 집중했습니다. 시험지 상으로는 언자상 88 88 80이었는데, 마킹실수를 거하게 한 것 같습니다. 언어논리는 실수한 포인트가 기억나는데, 자료해석은 기억이 나지 않습니다. 저처럼 막판에 몰아서 마킹하면 오히려 실수가 날 경우가 크기 때문에 적당히 끊어서 마킹하는 게 좋을 거 같습니다.   [헌법] 강의는 박철한 선생님의 올인원 강의를 듣고 이후 기출문제 풀이로 공부했습니다. 중간에 기출을 아무리 풀어도 이해가 되지 않아 기출인강을 따로 수강했었는데, 이때 크게 점수가 향상되었습니다. 이후 기본서와 기출문제를 계속 반복했고, 시험 한달전에 최신판례 책을 사서 공부했습니다. 최신판례 인강은 2회독을 했고, 따로 책을 3회독한 것 같습니다. 최신판례는 양이 많지 않아 주로 점심을 먹으면서 공부했던 기억이 있습니다. 헌법은 기출이 중요하기에 공기출 사이트에서 올해와 작년에 나온 시험문제를 전부 프린트해서 풀어봤습니다. 그리고 시험 3주 전부터는 기출문제나 모의고사를 풀 때 최대한 모르</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39651&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
         </is>
       </c>
     </row>
@@ -7132,6 +8026,11 @@
           <t>2-2 헌법헌법은 행정법에 비해 조문문제가 꽤 자주 나오고 단순암기해야할 사항이 많은 과목입니다. 단순암기는 시험끝물에 최대한 외운다고 생각하고 내용상 스토리가 있는 그런부분이 더 외우기 쉽기때문에 이런쪽을 우선 정복하는게 좋다고 생각합니다. 또한 헌법도 최신판례의 비중이 매우 크므로 최신판례 강의를 들으시는것을 추천드립니다.</t>
         </is>
       </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41937&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="55" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -7170,9 +8069,14 @@
           <t xml:space="preserve">2차 전공과목 헌법: 신동욱T 기본, 요약, 기출해설, 최신판례 + 신동욱T 기출 1, 2권 회독 반복(홀수번 짝수번 나눠서) + 최신판례 보충 단권화 + 해커스 2차 모의고사 국제정치학: 이상구T 기본, 요약), 기출해설, 동형, 실전모의 + 단권화 + 해커스 2차 모의고사 + 단행본 일부 참조(현대외교정책론(3판), 변환의 세계정치) + 국제기사 수시로 국제법: 이상구T 기본, 요약, 판례, 조약, 기출해설, 동형, 실전모의 + 단권화 + 해커스 2차 모의고사 + 단행본 일부 참조(신국제법강의(12판)) + 판례 정리 후 회독 반복 + 조약 반복 정독 제2외국어를 제외하면, 2차 과목에서 가장  공부하기 수월했던 것은 헌법이었습니다. 모든 직렬이 공통으로 치는 과목이라 정말 많은 기출이 쌓여 있어, 기출만 반복해도 빈출되거나 중요한 판례가 무엇인지 감을 잡을 수 있을 것입니다. 따라서, 다른 2차과목과 달리 개념 강의로는 틀만 대략 잡고, 최대한 빨리 기출문제 회독을 돌리면서 중요 판례를 최대한 많이 보고, 비슷해서 헷갈리는 판례들만 따로 모아 키워드 위주로 별도로 정리할 필요가 있습니다. 또, 3분의 1에서 거의 절반까지도 최신판례가 출제되므로, 시험 </t>
         </is>
       </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37348&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H5"/>
+  <autoFilter ref="A1:I5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7183,7 +8087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7194,6 +8098,7 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -7237,6 +8142,11 @@
           <t>발췌문2</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -7267,6 +8177,11 @@
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40692&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=31</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="55" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -7297,6 +8212,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40688&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=32</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="55" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -7331,6 +8251,11 @@
           <t>(행정학) 행정학의 경우에는 대부분의 수험생들이 그렇듯 시험 직전까지도 가장 자신이 없었습니다. 개념의 범위가 너무 넓고 항상 불의타 문제가 나오기 때문에 대비가 어렵다고 느꼈습니다. 행정학의 경우에는 여러 이론들에 대해서 묻기 때문에 이론 간의 비교에 집중하면서 공부하는게 큰 도움이 됐습니다. 간단하게 비유하자면 단순하게 (a 이론의 특성은 키가 작다) 이런 식으로 외우면  혼동이 생길 때가 많습니다. 왜냐하면 a 이론이 b이론과 비교했을 때는 키가 작았지만, 또 다른 c이론과 비교했을 때는 키가 큰 경우가 있기 때문입니다. 행정학은 법 과목의 판례들처럼 딱 정해진 것이 아니어서 어떤 대상과 비교하냐에 따라서 해당 이론의 특성이 아 다르고 어 다르기 때문에  (a 이론은 b 이론과 비교했을 때는 키가 작다) 이런 식으로 유사한 그룹의 개념들끼리 비교를 잡으면서 개념을 유연성 있게 정리하는게 많은 도움이 됐습니다.   (헌법)) 헌법의 경우 처음 기본 강의를 들을 때는 상대적으로 재밌다고 느꼈습니다. 왜냐하면 다양한 판례들이 나오고 아무래도 판례들이 우리 생활과 밀접해 있다 보니 이러한 경우도 있구나 하면서 상대적으로 즐겁게 기본강의를 들었습니다. 하지만 기</t>
         </is>
       </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39640&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="55" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -7373,6 +8298,11 @@
           <t>2. 헌법(92점) 교재 및 강의: 박철한 T 해커스 기본강의&amp;심화강의/ 신동욱T 기출문제집&amp; 기출문제강의, OX 문제집/ 김유향 T 최신판례집</t>
         </is>
       </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37722&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=88</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -7411,6 +8341,11 @@
           <t>*PSAT 언어논리 조윤정 선생님, 자료해석 김용훈 선생님, 상황판단 길규범 선생님 강의 수강하였고, 기본/심화/유형별 문제풀이까지 들었습니다. 특히 선생님들께서 이야기해주신대로 민경채 기출 11년도부터 시간 재면서 다 풀어봤고, 7급 기출도 20년도부터 시간 재면서 다 풀었습니다. 설명도 워낙 자세하게 잘해주시기 때문에 강의만 순서대로 따라간다면 PSAT은 크게 걱정하지 않아도 될 것 같습니다.  *헌법 황남기 선생님 강의 수강하였습니다. 기본이론은 시험을 2번 준비하면서 2번 다 수강하였고 기출강의는 23년 시험 떄와 겹치는게 많아서 23년 수험때만 수강하고 올해는 문제만 풀었습니다. 기본이론 수강 후에 진도에 맞춰서 기출문제 풀면서 1회독 한 후 다시 범위를 나눠서 기본서+기출서 2회독했습니다. 3회독부터는 기본서는 따로 보지 않고 기출서만 반복해서 봤습니다. 기출서는 총 5회독정도 한 것 같습니다. 기출서 회독하시는게 매우 중요하다고 생각하고 선생님이 강조하시는 것처럼 리갈 마인드로 문제를 푸는 것이 아니라 키워드를 기억해서 선지 다 읽지 않고도 바로바로 이게 어떤 판례였는지 기억해서 시간 줄이면서 문제 풀 수 있도록 준비하는 것이 중요한 것 같습니다</t>
         </is>
       </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39641&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="55" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -7449,6 +8384,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39745&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=45</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="55" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -7487,6 +8427,11 @@
           <t>1. 행정법100 *ㅆㄴ최종모의고사* 이미 국,지9급으로 완성되어 있어서 감만 유지하고 따로 강의를 듣지 않음. 솔직히 초시면 모르겠지만, 재시 또는 재재시라면 ㅆㄴ선생님의 교재사서 기본서의 날개 문제만 돌려서 외워도 충분함. 인강에서 ㅆㄴ선생님도 그렇게 말씀하셨고, 그말 믿고 그렇게 한 결과 3번다 100점 아니면 1개인가 틀렸던 듯함. 가장 핵심은 ㅆㄴ선생님 마무리 모의고사인가 8회짜리 있는데, 그게 정수임. 시간이 너무 없었기 때문에 행정법에 가장 시간을 덜 투자할 수 밖에 없었는데 그래서 기본서 읽을 때도 먼저 날개문제 읽어서 ox하고 틀린 것만 옆에 기본내용 가서 읽고 표시함. 이렇게 틀린 것만 해서 3번 돌림.(근데 초시이신 분들은 기출문제 열심히 돌리셔야함. 기출문제만이 살길입니다. 저는 이미 행정법의 거의 모든 기출문제를 알고 있었고, 잊어버리지 않기 위한 제일 효율적인 방법으로 이렇게 했습니다. 반면 재시거나 재재시이신 분들은 이렇게만 해도 충분함. 그만큼 ㅆㄴ선생님 교재는 완벽하고 믿고가면됨. 솔직히 행정법의 흐름을 아시거나 행정법에 대해서 이해도가 있으시다면 인강 안들어도 됩니다. 교재만 해도 완벽함. 그만큼 해설도 완벽하게 되어있습니다.</t>
         </is>
       </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39671&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="55" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -7525,6 +8470,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39639&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="55" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -7563,6 +8513,11 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39632&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="55" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -7601,6 +8556,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36995&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=90</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="55" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -7639,6 +8599,11 @@
           <t>[관세법] 관세사 수험시절, 이미 공부해봤었기 때문에 자신만만했으나...기출 풀어보면 점수가 잘 나오지 않는 ...과목이었습니다. 관세법 1타 강사 이명호 선생님 기본-심화과정까지 수강했고, 문제풀이는 저 혼자 진행했습니다. 선생님께서는 실제 시험에서 이 부분이 ~이렇게 나온다며 잘 체크해주십니다. 필기해주시는 부분 빠짐없이 다 적어서 외웠습니다. 또 목차노트를 만들었네요. 목차노트를 만들어서 목차옆에 생각나는대로 다 적어주고 맞는지 기본서랑 확인하는 방법으로 공부했습니다. 관세법의 경우 관세직 9급, 7급, 관세사 등 관세법 관련 기출문제 거의 다 뽑아서 풀고, 모르는 선지도 헌법/행정법과 마찬가지로 OX집을 만들어 외웠습니다.</t>
         </is>
       </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36762&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="55" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -7679,6 +8644,11 @@
       <c r="H13" s="3" t="inlineStr">
         <is>
           <t>9월 : 홍대겸 헌법 하프모의고사, 행정법/헌법 화력집중, 함수민 행정법각론특강, 행정법 문제풀이 특강</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39642&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
         </is>
       </c>
     </row>
@@ -7715,6 +8685,11 @@
           <t>2-2 헌법헌법은 행정법에 비해 조문문제가 꽤 자주 나오고 단순암기해야할 사항이 많은 과목입니다. 단순암기는 시험끝물에 최대한 외운다고 생각하고 내용상 스토리가 있는 그런부분이 더 외우기 쉽기때문에 이런쪽을 우선 정복하는게 좋다고 생각합니다. 또한 헌법도 최신판례의 비중이 매우 크므로 최신판례 강의를 들으시는것을 추천드립니다.</t>
         </is>
       </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41937&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="55" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -7757,6 +8732,11 @@
           <t>공부기간: 2025년 3월~ 2025년 9월  한국사와 영어는 따둔 상황이었고 제2외국어는 올해 5월에 취득하였습니다(대학 전공이라 어려움은 없었습니다). 전공과목들의 베이스가 하나도 없어서 외무영사직 해커스 0원 패스를 구매해서 수험생활을 시작하였습니다. 국제법, 국제정치학은 이상구 선생님, 헌법은 홍대겸 선생님 강의를 수강하였습니다. 공부는 하루에 7~8시간 정도를 했고 주에 2일은 열심히 노는데 집중하였습니다. 8월 중순부터는 쉬는 날 없이 8시간 정도 계속 하였습니다. 끝나고 나니 중간중간 잘 놀고 잘 쉬었던 것이 수험생활에서 멘탈관리에 많은 도움이 되었던 것 같습니다.  1. 1차 PSAT 96/100/92  저는 처음 PSAT 문제들을 풀어봤을때 크게 어렵지 않을 것 같다고 느껴서 강의는 수강하지 않았습니다. 1차 시험 한달 반 전부터 5급 문제들을 20문제씩 60분동안 푸는 연습을 하였고, 실전에서는 긴장이 많이 될 것 같아서 어느 상황에서든지 문제를 풀 수 있는는게 가장 중요하다고 생각을 하였고, 일부러 시끄러운 카페나 새로운 환경, 가장 피곤할때, 도서관에 도착하자마자 등 가장 집중이 되는 때에 60분동안 풀어보는 연습을 계속 했습니다. 시험</t>
         </is>
       </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41711&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="55" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -7791,6 +8771,11 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41691&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="55" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -7825,6 +8810,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39715&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="55" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -7863,9 +8853,14 @@
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39635&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H18"/>
+  <autoFilter ref="A1:I18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7876,7 +8871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7887,6 +8882,7 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -7930,6 +8926,11 @@
           <t>발췌문2</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -7964,6 +8965,11 @@
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41696&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="55" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -8002,6 +9008,11 @@
           <t>10월부터 기본강의를 듣고 시험 직전에 법령특강, 최신판례특강을 들었습니다. 기본강의를 2배속으로 빠르게 듣고 듣는 중에 기출문제를 바로바로 풀었습니다. 기본강의 끝낸 후에는 기출 회독을 계속 돌렸고, 강의 중에 회독 돌리는 방법을 알려주셔서 시험 한 달 전까지는 계속 기출만 보았으며, 한 달 남았을 때는 법령과 최신판례를 같이 보았습니다. 기출을 많이 보다보면 기본서를 후에 회독 돌릴 때에는 생소한 부분만 보이기 때문에 더 빠르게 회독을 돌릴 수 있었습니다. 황남기 선생님은 특별히 외우는 방법을 알려주시지는 않지만 판례 배경 등을 설명해주셔서 더 기억에 남을 수 있었던 것 같습니다. 또한 비슷한 주제로 위헌, 합헌으로 나뉘는 판례들은 암기하기 위해 따로 노트를 만들었는데 시험 직전에 다시 정리했던 것이 실제 시험장에서 너무 큰 도움이 되었습니다.   (행정법-황남기 선생님, 함수민 선생님) 헌법을 먼저 들었기 때문에 행정법 또한 황남기 선생님을 선택해서 들었습니다. 헌법과 공부방법은 비슷하나 행정법각론 부분은 시험 3달 전에 전년도 강의를 가볍게 황남기 선생님 강의로 듣고 2달 전에는 당해연도 함수민 선생님 강의를 들었고, 시험 한 달 전부터는 각론기출문제</t>
         </is>
       </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39681&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="55" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -8044,6 +9055,11 @@
           <t>(2) 헌법 [강의] 황남기쌤 헌법 기본이론 23년, 24년 각 1회 수강 [교재] 황남기쌤 기본서 3회독(인강 수강 포함) [교재] 황남기쌤 기출문제집 9회독 [교재] 경간 소간 국회직 등등 각종 시행처 최신기출</t>
         </is>
       </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39626&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="55" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -8082,6 +9098,11 @@
           <t>*PSAT 언어논리 조윤정 선생님, 자료해석 김용훈 선생님, 상황판단 길규범 선생님 강의 수강하였고, 기본/심화/유형별 문제풀이까지 들었습니다. 특히 선생님들께서 이야기해주신대로 민경채 기출 11년도부터 시간 재면서 다 풀어봤고, 7급 기출도 20년도부터 시간 재면서 다 풀었습니다. 설명도 워낙 자세하게 잘해주시기 때문에 강의만 순서대로 따라간다면 PSAT은 크게 걱정하지 않아도 될 것 같습니다.  *헌법 황남기 선생님 강의 수강하였습니다. 기본이론은 시험을 2번 준비하면서 2번 다 수강하였고 기출강의는 23년 시험 떄와 겹치는게 많아서 23년 수험때만 수강하고 올해는 문제만 풀었습니다. 기본이론 수강 후에 진도에 맞춰서 기출문제 풀면서 1회독 한 후 다시 범위를 나눠서 기본서+기출서 2회독했습니다. 3회독부터는 기본서는 따로 보지 않고 기출서만 반복해서 봤습니다. 기출서는 총 5회독정도 한 것 같습니다. 기출서 회독하시는게 매우 중요하다고 생각하고 선생님이 강조하시는 것처럼 리갈 마인드로 문제를 푸는 것이 아니라 키워드를 기억해서 선지 다 읽지 않고도 바로바로 이게 어떤 판례였는지 기억해서 시간 줄이면서 문제 풀 수 있도록 준비하는 것이 중요한 것 같습니다</t>
         </is>
       </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39641&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -8120,6 +9141,11 @@
           <t>헌법,행정법- 홍대겸 선생님 저는 1년차에 헌법과 행정법 강의를 다른 선생님들의 강의로 수강하였습니다. 그런데 너무나 강의 수도 많고 책도 두꺼워서 공부하기도 어려웠을 뿐만 아니라 내용들을 저의 것으로 만드는 복습 시간이 너무 오래걸려서 공부를 포기하고 싶은 마음이 많이 들었습니다. 하루하루 진도는 나아가는데 모르는 것 투성이에 다음 진도 이해하는데에도 어려움이 있어서 정말 많이 힘들었습니다. 그렇게 첫 해 시험이 끝난 후, 지푸라기라도 잡고 싶은 심정으로 홍대겸 선생님의 강의를 선택하였는데 이 선택이 제가 수험기간중에 했던 가장 좋은 선택이었던 것 같습니다. 우선 책과 강의가 굉장히 컴팩트한 것이 수강생의 심적인 부담을 굉장히 줄여주었습니다. 선생님의 커리큘럼 대로만 따라가더라도 틈틈이 복습하면서 공부를 할 수 있었습니다. 그리고 무엇보다 학생들이 이해하기 쉽도록 예시를 들어주시고, 수업 중간중간에 동기부여가 되는 말씀도 해주시면서 포기하는 마음이 들지 않게끔 학생들을 잘 이끌어주십니다. 1차 시험 이후 2차 전공 시험 전에는 그동안의 내용을 계속해서 까먹지 않게 복습하면서 선생님이 준비해주시는 개인 모의고사를 풀며 마무리한다면 행정법과 헌법에서 크게 어렵</t>
         </is>
       </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41963&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="55" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -8162,6 +9188,11 @@
           <t>기본강의 1회독, 기출문제집 4회독(아이패드에 기록하며 왼쪽위에 네모칸에 틀린문제들 기록), 기본서 회독은 10회독씩 넘어가면서 카운트X, 헌법과 행정법은 기출문제 해설까지 수강, 관세법과 무역학은 기출문제 해설은 패스하고 기본서 회독에 집중. 결국 마지막에 가서는 회독이 가장 중요하다고 생각함. 헌법, 행정법은 최신판례및 기출위주의 회독을 중점적으로 하고 관세법, 무역학의 경우는 문제는 본인의 실력을 체크하는 식으로 활용하면서 기본서를 자세히 꼼꼼하게 암기하는 느낌으로 회독하면 충분히 합격할 수 있다고 생각함.</t>
         </is>
       </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41936&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="55" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -8196,6 +9227,11 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41690&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="55" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -8238,6 +9274,11 @@
           <t>2024년에는 1차 60일 전부터 시작했습니다. 작년에 합격한 경험이 있기에 하루에 한과목씩 모의고사(주로 5급)을 풀었고, 시험 2주전에서야 매일 모의고사를 치거나 온종일 PSAT에 집중했습니다. 시험지 상으로는 언자상 88 88 80이었는데, 마킹실수를 거하게 한 것 같습니다. 언어논리는 실수한 포인트가 기억나는데, 자료해석은 기억이 나지 않습니다. 저처럼 막판에 몰아서 마킹하면 오히려 실수가 날 경우가 크기 때문에 적당히 끊어서 마킹하는 게 좋을 거 같습니다.   [헌법] 강의는 박철한 선생님의 올인원 강의를 듣고 이후 기출문제 풀이로 공부했습니다. 중간에 기출을 아무리 풀어도 이해가 되지 않아 기출인강을 따로 수강했었는데, 이때 크게 점수가 향상되었습니다. 이후 기본서와 기출문제를 계속 반복했고, 시험 한달전에 최신판례 책을 사서 공부했습니다. 최신판례 인강은 2회독을 했고, 따로 책을 3회독한 것 같습니다. 최신판례는 양이 많지 않아 주로 점심을 먹으면서 공부했던 기억이 있습니다. 헌법은 기출이 중요하기에 공기출 사이트에서 올해와 작년에 나온 시험문제를 전부 프린트해서 풀어봤습니다. 그리고 시험 3주 전부터는 기출문제나 모의고사를 풀 때 최대한 모르</t>
         </is>
       </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39651&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="55" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -8280,6 +9321,11 @@
           <t>공부기간: 2025년 3월~ 2025년 9월  한국사와 영어는 따둔 상황이었고 제2외국어는 올해 5월에 취득하였습니다(대학 전공이라 어려움은 없었습니다). 전공과목들의 베이스가 하나도 없어서 외무영사직 해커스 0원 패스를 구매해서 수험생활을 시작하였습니다. 국제법, 국제정치학은 이상구 선생님, 헌법은 홍대겸 선생님 강의를 수강하였습니다. 공부는 하루에 7~8시간 정도를 했고 주에 2일은 열심히 노는데 집중하였습니다. 8월 중순부터는 쉬는 날 없이 8시간 정도 계속 하였습니다. 끝나고 나니 중간중간 잘 놀고 잘 쉬었던 것이 수험생활에서 멘탈관리에 많은 도움이 되었던 것 같습니다.  1. 1차 PSAT 96/100/92  저는 처음 PSAT 문제들을 풀어봤을때 크게 어렵지 않을 것 같다고 느껴서 강의는 수강하지 않았습니다. 1차 시험 한달 반 전부터 5급 문제들을 20문제씩 60분동안 푸는 연습을 하였고, 실전에서는 긴장이 많이 될 것 같아서 어느 상황에서든지 문제를 풀 수 있는는게 가장 중요하다고 생각을 하였고, 일부러 시끄러운 카페나 새로운 환경, 가장 피곤할때, 도서관에 도착하자마자 등 가장 집중이 되는 때에 60분동안 풀어보는 연습을 계속 했습니다. 시험</t>
         </is>
       </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41711&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="55" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -8318,9 +9364,14 @@
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41680&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H11"/>
+  <autoFilter ref="A1:I11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8331,7 +9382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8342,6 +9393,7 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -8385,6 +9437,11 @@
           <t>발췌문2</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -8415,6 +9472,11 @@
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41486&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=5</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="55" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -8451,6 +9513,11 @@
       <c r="H3" s="3" t="inlineStr">
         <is>
           <t>10월부터 기본강의를 듣고 시험 직전에 법령특강, 최신판례특강을 들었습니다. 기본강의를 2배속으로 빠르게 듣고 듣는 중에 기출문제를 바로바로 풀었습니다. 기본강의 끝낸 후에는 기출 회독을 계속 돌렸고, 강의 중에 회독 돌리는 방법을 알려주셔서 시험 한 달 전까지는 계속 기출만 보았으며, 한 달 남았을 때는 법령과 최신판례를 같이 보았습니다. 기출을 많이 보다보면 기본서를 후에 회독 돌릴 때에는 생소한 부분만 보이기 때문에 더 빠르게 회독을 돌릴 수 있었습니다. 황남기 선생님은 특별히 외우는 방법을 알려주시지는 않지만 판례 배경 등을 설명해주셔서 더 기억에 남을 수 있었던 것 같습니다. 또한 비슷한 주제로 위헌, 합헌으로 나뉘는 판례들은 암기하기 위해 따로 노트를 만들었는데 시험 직전에 다시 정리했던 것이 실제 시험장에서 너무 큰 도움이 되었습니다.   (행정법-황남기 선생님, 함수민 선생님) 헌법을 먼저 들었기 때문에 행정법 또한 황남기 선생님을 선택해서 들었습니다. 헌법과 공부방법은 비슷하나 행정법각론 부분은 시험 3달 전에 전년도 강의를 가볍게 황남기 선생님 강의로 듣고 2달 전에는 당해연도 함수민 선생님 강의를 들었고, 시험 한 달 전부터는 각론기출문제</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39681&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
         </is>
       </c>
     </row>
@@ -8483,6 +9550,11 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39664&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="55" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -8521,6 +9593,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39745&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=45</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -8559,6 +9636,11 @@
           <t>2. 전공필기시험    5급을 준비했다보니 7급 국제법과 국제정치학은 꽤나 준비가 되어있던 편이라고 생각했었습니다만, 아니었습니다. 국제법은 그럭저럭 방어가 됐지만, 국제정치학에서 확실히 5급 논술형 시험과 7급 객관식 시험의 차이를 크게 느꼈습니다. 2024년 외무영사직 시험에서 국제법 88점, 국제정치학 56점이라는 점수가 이를 증명하죠. 그리고 헌법도 5급 시험에서처럼 60점 이상만을 목표로 하는 시험이 아니게 되며, 추가적인 공부가 필요해졌습니다. 그래서 이때 해커스 외무영사직 패스를 이용하기로 결정하고, 이상구 선생님과 황남기 선생님를 알게 됐습니다.</t>
         </is>
       </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41922&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="55" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -8601,6 +9683,11 @@
           <t>공부기간: 2025년 3월~ 2025년 9월  한국사와 영어는 따둔 상황이었고 제2외국어는 올해 5월에 취득하였습니다(대학 전공이라 어려움은 없었습니다). 전공과목들의 베이스가 하나도 없어서 외무영사직 해커스 0원 패스를 구매해서 수험생활을 시작하였습니다. 국제법, 국제정치학은 이상구 선생님, 헌법은 홍대겸 선생님 강의를 수강하였습니다. 공부는 하루에 7~8시간 정도를 했고 주에 2일은 열심히 노는데 집중하였습니다. 8월 중순부터는 쉬는 날 없이 8시간 정도 계속 하였습니다. 끝나고 나니 중간중간 잘 놀고 잘 쉬었던 것이 수험생활에서 멘탈관리에 많은 도움이 되었던 것 같습니다.  1. 1차 PSAT 96/100/92  저는 처음 PSAT 문제들을 풀어봤을때 크게 어렵지 않을 것 같다고 느껴서 강의는 수강하지 않았습니다. 1차 시험 한달 반 전부터 5급 문제들을 20문제씩 60분동안 푸는 연습을 하였고, 실전에서는 긴장이 많이 될 것 같아서 어느 상황에서든지 문제를 풀 수 있는는게 가장 중요하다고 생각을 하였고, 일부러 시끄러운 카페나 새로운 환경, 가장 피곤할때, 도서관에 도착하자마자 등 가장 집중이 되는 때에 60분동안 풀어보는 연습을 계속 했습니다. 시험</t>
         </is>
       </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41711&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="55" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -8639,9 +9726,14 @@
           <t xml:space="preserve">2차 전공과목 헌법: 신동욱T 기본, 요약, 기출해설, 최신판례 + 신동욱T 기출 1, 2권 회독 반복(홀수번 짝수번 나눠서) + 최신판례 보충 단권화 + 해커스 2차 모의고사 국제정치학: 이상구T 기본, 요약), 기출해설, 동형, 실전모의 + 단권화 + 해커스 2차 모의고사 + 단행본 일부 참조(현대외교정책론(3판), 변환의 세계정치) + 국제기사 수시로 국제법: 이상구T 기본, 요약, 판례, 조약, 기출해설, 동형, 실전모의 + 단권화 + 해커스 2차 모의고사 + 단행본 일부 참조(신국제법강의(12판)) + 판례 정리 후 회독 반복 + 조약 반복 정독 제2외국어를 제외하면, 2차 과목에서 가장  공부하기 수월했던 것은 헌법이었습니다. 모든 직렬이 공통으로 치는 과목이라 정말 많은 기출이 쌓여 있어, 기출만 반복해도 빈출되거나 중요한 판례가 무엇인지 감을 잡을 수 있을 것입니다. 따라서, 다른 2차과목과 달리 개념 강의로는 틀만 대략 잡고, 최대한 빨리 기출문제 회독을 돌리면서 중요 판례를 최대한 많이 보고, 비슷해서 헷갈리는 판례들만 따로 모아 키워드 위주로 별도로 정리할 필요가 있습니다. 또, 3분의 1에서 거의 절반까지도 최신판례가 출제되므로, 시험 </t>
         </is>
       </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37348&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H8"/>
+  <autoFilter ref="A1:I8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8652,7 +9744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8663,6 +9755,7 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -8706,6 +9799,11 @@
           <t>발췌문2</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -8740,6 +9838,11 @@
           <t>3. 나의 수험 계획표 다양한 방법들을 시도해보았지만, 저는 앞서 말했던 것처럼 하루에 4과목을 전부 보는 방식이 저에게 잘 맞아서 그렇게 진행했습니다. 우선 공부는 8시 이전에 열품타 착석스터디를 통해 스스로를 컨트롤 하며 시작했습니다. 행정학 2시간(이때 말하는 시간은 최소 시간입니다. 인강이나 문풀 상황에 따라 10-15분 정도는 더 진행할 때가 많습니다) -&gt; 행정법 1시간 -&gt; 약 12시쯤 점심식사 및 식곤증을 물리치기 위한 샤워 등 재정비 -&gt; 2시 쯤. 경제학 2시간 (그나마 손을 가장 많이 써서 덜 졸려서 이걸 이때 했습니다) -&gt; 1시간 정도 행정법 추가 공부 -&gt; 6시쯤 저녁 식사 후 휴식 -&gt; 2시간 동안 헌법 마무리</t>
         </is>
       </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41729&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="55" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -8776,6 +9879,11 @@
       <c r="H3" s="3" t="inlineStr">
         <is>
           <t>1) 4월~6월 : 기본 이론 강의 수강 행정법, 헌법 (홍대겸)/ 행정학 (서현) 기본 강의를 수강하였습니다. 두 분을 선택한 계기는 좀 불순한데, 일단 교재가 없어도 수업을 들을 수 있게 판서 혹은 PPT를 활용하는 수업방식이 마음에 들었습니다. 불순한 계기와 달리, 결과적으로 두 분을 선택하여서 좋은 결과를 얻을 수 있었습니다. 홍대겸 선생님의 가장 큰 장점이자 매력은 컴팩트함입니다. 법학을 이해하는 데 필요한 기본적인 논리는 놓치지 않고 설명해주시되 디테일을 과감하게 생략하며 빠르게 진도를 나가시는 타입이십니다. 그래서 강의 회차와 시간 모두 짧습니다. 가볍고 빠르게 나아가는 수업은 빠르게 기본 이론을 배우고 싶었던 당시의 저에게는 최고의 선택이었습니다. 설명도 가능한 직관적이고 단정적으로 하셔서 법학이 까다롭고 어렵다는 선입견을 깨시고 부담을 많이 덜어주셨습니다. "빠른 1회독" 강의도 큰 도움이 되었습니다. 기초 이론을 가볍게 맛본 수험생을 대상으로 하는 강의인데, 기초 강의 때는 생략하였던 변칙적인 판례를 설명해주시기도 하고, 말 그대로 빠르게 행정법 전체를 복습할 수 있습니다. 서현 선생님의 장점은 체계성입니다. 그동안의 기출 경향을 모두 꿰고</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41687&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
         </is>
       </c>
     </row>
@@ -8808,6 +9916,11 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41368&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=10</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="55" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -8838,6 +9951,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39633&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -8868,6 +9986,11 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39340&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=49</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="55" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -8902,6 +10025,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37336&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="55" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -8932,6 +10060,11 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37288&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="55" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -8968,6 +10101,11 @@
       <c r="H9" s="3" t="inlineStr">
         <is>
           <t>헌법&amp;행정법은 황남기 선생님 강의 들으면서 기본서 위주보다는 기출을 계속 무한으로 돌렸습니다.</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37101&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=90</t>
         </is>
       </c>
     </row>
@@ -9000,6 +10138,11 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36908&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="55" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -9034,6 +10177,11 @@
           <t>안녕하세요. 처음 공무원 준비를 시작할 때에는 저의 계획이 정말 실현될 수 있을지 저 스스로도 의심하게 되고 막막하였지만 결국 제가 올해 합격을 하게 되었습니다. 저는 단기 합격을 위한 계획을 세웠습니다(5개월 정도). 과정을 이야기하자면, 먼저 저는 1월 말 정도부터 5급 1차 시험을 준비하였습니다. 피셋 공부와 헌법 1회독을 이 시기에 처음 하게 되었습니다. 하지만 1차 시험에서 떨어졌고, 그 충격으로 5월 8일까지 공부를 안하고 놀기만 했습니다. 어버이날이 지나고 더는 부모님께 손벌리기가 싫었고, 사기업에 종사하는 것보다는 국가를 위한 일을 하고자 하는 마음이 있었기 때문에 7급 공무원을 준비하게 되었습니다(진짜입니다). 다행히 1차 시험은 1월에 5급 시험을 준비했던 경험으로 4일 정도 공부하여 붙을 수 있었습니다. 이후 2차 시험을 위해 제가 먼저 준비를 시작했던 과목은 경제학이었습니다. 아무래도 이해가 필요한 과목이고 휘발성이 다른 암기과목들에 비해 낮다고 생각을 하였기 때문에 가장 먼저 준비를 했습니다. 경제학은 일단 처음 들을 때에는 당연히 이해가 잘 안되지만 저는 이해를 해야 넘어가는 스타일이라 조금 까다로웠습니다. 김종국 선생님의 강의를 들</t>
         </is>
       </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36756&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="55" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -9068,6 +10216,11 @@
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36754&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="55" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -9106,6 +10259,11 @@
           <t>- 헌법 : 신동욱 선생님 공시 진입하려고 헌법 기본서를 주문해 놓고 뜨악했더랬죠, 이 두꺼운 책을 머릿속에 우겨넣을 생각을 하니 공무원 준비를 괜히 했나 생각이 들 정도였습니다. 하지만 선생님 강의 천천히 따라가니 결국엔 큰 흐름이 잡혀요. 왜 사람들이 헌법 회독이 중요하다. 회독회독 그렇게 얘기하는지 처음엔 몰랐는데애초에 1300쪽 가까이 되는 이 방대한 분량을 하나하나 꼼꼼히 이해하면서 다른과목 하듯이 진도나간다는게 욕심이었습니다. 팁 드리자면 처음 1회차는 강의 틀어놓고 책정리하면서, 흐름 (대충 이런게 있구나) 느끼는데 집중하고</t>
         </is>
       </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36748&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="55" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -9140,6 +10298,11 @@
       </c>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=34959&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=140</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="55" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -9174,6 +10337,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39729&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="55" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -9208,6 +10376,11 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39634&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="55" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -9246,6 +10419,11 @@
           <t>-헌법 지역인재7급을 위한 헌법 강의는 따로 마련된 것이 없었기 때문에 저는 신동욱 선생님의 법원직 헌법 강의를 수강하였습니다. 법쪽으로 전혀 지식이 없는 상태라 입문특강부터 차근차근 수강하였는데, 신동욱 선생님께서 입문특강에서 정말 잘 설명해주셔서 헌법에 대한 기초 지식뿐만 아니라 관심도가 많이 상승했던 것 같습니다. 기본이론을 들으면서도 많은 판례들과 함께 설명해주셔서 각 판례들의 구체적인 스토리를 들으며 재밌게 공부하였던 것 같습니다. 헌법 노베이스이신 분들께 신동욱 선생님의 헌법 강의 강추 드립니다!</t>
         </is>
       </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=34803&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=141</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="55" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -9286,6 +10464,11 @@
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>-헌법 지역인재7급을 위한 헌법 강의는 따로 마련된 것이 없었기 때문에 저는 신동욱 선생님의 법원직 헌법 강의를 수강하였습니다. 법쪽으로 전혀 지식이 없는 상태라 입문특강부터 차근차근 수강하였는데, 신동욱 선생님께서 입문특강에서 정말 잘 설명해주셔서 헌법에 대한 기초 지식뿐만 아니라 관심도가 많이 상승했던 것 같습니다. 기본이론을 들으면서도 많은 판례들과 함께 설명해주셔서 각 판례들의 구체적인 스토리를 들으며 재밌게 공부하였던 것 같습니다. 헌법 노베이스이신 분들께 신동욱 선생님의 헌법 강의 강추 드립니다!</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=34802&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=141</t>
         </is>
       </c>
     </row>
@@ -9322,6 +10505,11 @@
           <t>1차 피셋은 작년 합격 경험이 있어서 7월부터 시작하였고 6월까지는 2차과목 위주로 공부하였습니다. 하루를 9-12시, 13-17시, 18-22시로 3등분 하여 헌법, 행정법, 관세법을 공부하였습니다.</t>
         </is>
       </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39769&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=45</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="55" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -9360,6 +10548,11 @@
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39739&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=45</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="55" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -9394,6 +10587,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39623&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="55" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -9430,6 +10628,11 @@
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>- 헌법: 헌법은 제가 제일 재미있게 공부한 과목이었습니다. 맨 처음 교재가 배송되어 왔을 때는 그 엄청난 책 두께에 잠시 주눅이 들었었지만, 강의를 들으며 차근차근 따라나가고 판례를 반복해서 읽다보면 어느새 진도가 쭉 나가있더라구요. 저는 신동욱 선생님의 강의를 들었습니다. 신동욱 선생님은 차분하게 강의를 진행하시면서도 중간중간 위트 있는 농담으로 강의가 지루하지 않게 해주셔서 너무 좋았습니다. 커리큘럼 자체도 깔끔하기 때문에 신동욱 선생님의 강의를 들으면서 판례를 중심으로 복습을 꾸준히 해준다면 큰 무리없이 헌법 고득점이 가능할 것 같습니다. 특히 선생님의 최신판례특강은 꼭 듣는 것을 추천합니다.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39652&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
         </is>
       </c>
     </row>
@@ -9462,6 +10665,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=34832&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=141</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="55" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -9498,6 +10706,11 @@
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t>- 헌법과 아주 유사하게 인강 수강 후 당일 2회독 확보, 다음날까지 3회독 확보하는 식으로 학습</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39802&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=45</t>
         </is>
       </c>
     </row>
@@ -9534,6 +10747,11 @@
           <t>그래서 다른 전공과목은 뒷전에 두고 피셋을 열심히 준비했었는데, 제 생각에는 이때 많이 올려둔 피셋 실력 덕에 1차는 매년 합격할 수 있었던 것 같습니다. 처음에는 외영직 프리패스에 포함되어 있는 조은정, 김용훈, 길규범 선생님의 강의를 커리 순서대로 다 따라가며 듣고, 개인적으로 5급 기출을 여러번 풀었습니다. 헌법은 제가 가장 많은 노력을 투자했는데도 가장 낮은 점수를 받은 과목입니다. 헌법을 유난히 어려워하는건 제가 조금 특이 케이스 인 것 같긴 하지만, 혹시나 저 같은 수험생분들은 자신에게 맞는 강사님을 찾는 것이 중요하기 때문에 여러 강사님들의 시범강의나 무료제공 강의들을 한 번씩 들어보고 결정해보시는 것도 괜찮을 것 같습니다.</t>
         </is>
       </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39646&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="55" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -9574,6 +10792,11 @@
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t>-헌법도 초시 때 기본 강의 듣고 후로는 강의 안 듣고 혼자 학습, 이 때 교재: 간추린 로스쿨 핵심강의 헌법</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39628&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
         </is>
       </c>
     </row>
@@ -9606,6 +10829,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36759&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="55" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -9636,6 +10864,11 @@
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38613&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=71</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="55" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
@@ -9670,6 +10903,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35581&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=126</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="55" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -9704,6 +10942,11 @@
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35554&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=126</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="55" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
@@ -9742,9 +10985,14 @@
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39644&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H31"/>
+  <autoFilter ref="A1:I31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>